--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_correct_values.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_correct_values.xlsx
@@ -41,14 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -59,8 +59,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,7 +146,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -158,10 +164,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -775,10 +781,10 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>582.9</v>
+        <v>582.2</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="E4" s="11" t="n">
         <v>13.6</v>
@@ -793,13 +799,13 @@
         <v>13.1</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>45.1</v>
+        <v>2.8</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>14.2</v>
+        <v>1.2</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>11.7</v>
@@ -808,7 +814,7 @@
         <v>13.1</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>87</v>
@@ -826,16 +832,14 @@
         <v>16.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>152</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v>120.7</v>
+        <v>52</v>
+      </c>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="3" t="n">
+        <v>107.1</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
@@ -854,7 +858,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>288.9</v>
+        <v>388.5</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>24</v>
@@ -868,32 +872,32 @@
       <c r="G5" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="H5" s="8" t="n">
-        <v>12.3</v>
+      <c r="H5" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>12.7</v>
+        <v>0.8</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.4</v>
+        <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>16.1</v>
+        <v>18.9</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>19.4</v>
+        <v>18.9</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>22.4</v>
@@ -901,7 +905,7 @@
       <c r="R5" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="S5" s="8" t="n">
+      <c r="S5" s="14" t="n">
         <v>16.7</v>
       </c>
       <c r="T5" s="3" t="n">
@@ -920,7 +924,7 @@
         <v>18.4</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>75.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>6</v>
@@ -942,13 +946,13 @@
         <v>508.9</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>23.2</v>
+        <v>24.1</v>
       </c>
       <c r="E6" s="11" t="n">
         <v>12.8</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>11.2</v>
@@ -965,14 +969,14 @@
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="8" t="n">
+      <c r="L6" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="M6" s="3" t="n">
-        <v>13</v>
+      <c r="M6" s="14" t="n">
+        <v>30.9</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>1.9</v>
+        <v>19.5</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>92</v>
@@ -981,7 +985,7 @@
         <v>1.2</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>25.6</v>
+        <v>23.6</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>17.9</v>
@@ -998,17 +1002,17 @@
       <c r="V6" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="W6" s="8" t="n">
+      <c r="W6" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X6" s="8" t="n">
-        <v>18.1</v>
+      <c r="X6" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>87</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1026,72 +1030,70 @@
       <c r="C7" s="3" t="n">
         <v>512.9</v>
       </c>
-      <c r="D7" s="11" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>18.98</v>
+      <c r="D7" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr"/>
+      <c r="F7" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="14" t="n">
         <v>12</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.4</v>
+        <v>11.4</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>3.4</v>
+        <v>8.4</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="M7" s="8" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>18.8</v>
+      <c r="M7" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="N7" s="14" t="n">
+        <v>52.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>593</v>
+        <v>293</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q7" s="3" t="inlineStr"/>
       <c r="R7" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>59.1</v>
       </c>
-      <c r="U7" s="8" t="n">
+      <c r="U7" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="W7" s="8" t="n">
+      <c r="W7" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.1</v>
+        <v>21</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1113,10 +1115,10 @@
         <v>21.6</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>7.7</v>
@@ -1131,7 +1133,7 @@
         <v>1.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>27.2</v>
+        <v>6.4</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>15.1</v>
@@ -1140,10 +1142,10 @@
         <v>14.2</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.8</v>
@@ -1154,14 +1156,14 @@
       <c r="R8" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="S8" s="8" t="n">
+      <c r="S8" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>76</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>3.8</v>
+        <v>35.8</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>17.1</v>
@@ -1188,71 +1190,69 @@
       <c r="C9" s="3" t="n">
         <v>2224.9</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="9" t="n">
         <v>118.5</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="F9" s="11" t="n">
+      <c r="E9" s="9" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="F9" s="9" t="n">
         <v>93.09999999999999</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>881.5</v>
+        <v>20.9</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>10.5</v>
-      </c>
+        <v>63.1</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="n">
-        <v>16.9</v>
+        <v>260.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>31.1</v>
+        <v>51.1</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>19.4</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>60.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>86</v>
+        <v>16.6</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>959</v>
+        <v>1590.1</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1194</v>
+        <v>114</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>88.09999999999999</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>6.8</v>
+        <v>86.8</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>2162.6</v>
+        <v>212.6</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>22</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>959</v>
+        <v>94</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>89.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>419.8</v>
+        <v>848.1</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>2</v>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>449</v>
+        <v>495</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>23.7</v>
@@ -1289,12 +1289,14 @@
         <v>12.6</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
+        <v>3.8</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>14.7</v>
       </c>
@@ -1305,22 +1307,22 @@
         <v>15.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>91.8</v>
+        <v>921.8</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>1.3</v>
+        <v>113.8</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>85.8</v>
+        <v>9</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="S10" s="3" t="n">
-        <v>17.2</v>
+      <c r="S10" s="14" t="n">
+        <v>78.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>62.9</v>
+        <v>62.8</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>10.6</v>
@@ -1354,58 +1356,58 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>221.8</v>
-      </c>
-      <c r="D11" s="3" t="n">
+        <v>924.2</v>
+      </c>
+      <c r="D11" s="11" t="n">
         <v>22.5</v>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F11" s="3" t="n">
+      <c r="E11" s="11" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F11" s="11" t="n">
         <v>18.1</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="K11" s="8" t="n">
-        <v>10.8</v>
+      <c r="K11" s="3" t="n">
+        <v>10.2</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>14</v>
+        <v>14.8</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>11.8</v>
+        <v>18.1</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="P11" s="8" t="n">
-        <v>10.4</v>
+        <v>885</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="S11" s="8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="S11" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>28.4</v>
+        <v>82</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>10.6</v>
@@ -1449,9 +1451,9 @@
         <v>17.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="H12" s="8" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="H12" s="14" t="n">
         <v>13</v>
       </c>
       <c r="I12" s="3" t="n">
@@ -1464,16 +1466,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>83.5</v>
+        <v>14.5</v>
+      </c>
+      <c r="M12" s="14" t="n">
+        <v>38.5</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>12</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>92.8</v>
+        <v>12.8</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.2</v>
@@ -1494,7 +1496,7 @@
         <v>6.2</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>16</v>
+        <v>1.6</v>
       </c>
       <c r="W12" s="3" t="n">
         <v>14.8</v>
@@ -1503,7 +1505,7 @@
         <v>17.5</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>240.8</v>
+        <v>18.4</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>3.8</v>
@@ -1525,7 +1527,7 @@
         <v>322</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="E13" s="11" t="n">
         <v>13.8</v>
@@ -1534,10 +1536,10 @@
         <v>18.7</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>28.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>15.1</v>
+        <v>13.1</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.4</v>
@@ -1549,7 +1551,7 @@
         <v>15.7</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>14.4</v>
@@ -1561,19 +1563,19 @@
         <v>94.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q13" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q13" s="14" t="n">
         <v>15.8</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>1.6</v>
+        <v>16.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>90.5</v>
+        <v>20.5</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>6.2</v>
@@ -1585,10 +1587,10 @@
         <v>15.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>15.1</v>
+        <v>1.5</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.8</v>
@@ -1612,26 +1614,26 @@
       <c r="D14" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="14" t="n">
         <v>13.4</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>17.8</v>
+        <v>11.4</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>21.4</v>
+        <v>71.5</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>11.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>26.8</v>
+        <v>86.8</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>14.4</v>
@@ -1649,22 +1651,22 @@
         <v>1</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>21.3</v>
+        <v>2.8</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>18.1</v>
+        <v>1.8</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>7.2</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>14.8</v>
@@ -1698,11 +1700,11 @@
       <c r="E15" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="F15" s="13" t="n">
-        <v>78.3</v>
+      <c r="F15" s="3" t="n">
+        <v>7.5</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>12.6</v>
@@ -1711,7 +1713,7 @@
         <v>1.2</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>5.9</v>
@@ -1720,7 +1722,7 @@
         <v>14.2</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>148.1</v>
+        <v>13.8</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>15.5</v>
@@ -1729,7 +1731,7 @@
         <v>96.8</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>19.8</v>
@@ -1775,73 +1777,73 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1972.2</v>
-      </c>
-      <c r="D16" s="10" t="n">
+        <v>1973.2</v>
+      </c>
+      <c r="D16" s="9" t="n">
         <v>114.8</v>
       </c>
-      <c r="E16" s="10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>91.09999999999999</v>
+      <c r="E16" s="9" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>96</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>47.4</v>
+        <v>17.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>649.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>5.9</v>
+        <v>1.2</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>6.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>191.2</v>
+        <v>73.2</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>69.40000000000001</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1164.2</v>
+        <v>15.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>64.8</v>
+        <v>4.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>96.90000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>83.8</v>
+        <v>61.4</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>164.8</v>
+        <v>3945.2</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>84.5</v>
+        <v>84</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>180.6</v>
+        <v>18.6</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>85.09999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>488.8</v>
+        <v>428.8</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>2.8</v>
@@ -1860,19 +1862,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>225</v>
-      </c>
-      <c r="D17" s="10" t="n">
+        <v>1469.4</v>
+      </c>
+      <c r="D17" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="E17" s="13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>14.1</v>
+      <c r="E17" s="9" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>4.8</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>9.5</v>
+        <v>0.9</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.9</v>
@@ -1880,11 +1882,11 @@
       <c r="I17" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J17" s="8" t="n">
+      <c r="J17" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>14.6</v>
@@ -1893,7 +1895,7 @@
         <v>13.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>19.8</v>
+        <v>15.8</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>92.90000000000001</v>
@@ -1905,16 +1907,16 @@
         <v>19.8</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>18.9</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>16.9</v>
@@ -1947,38 +1949,38 @@
       <c r="C18" s="3" t="n">
         <v>428.8</v>
       </c>
-      <c r="D18" s="13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>18.1</v>
+      <c r="D18" s="11" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>18.9</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>12.4</v>
+        <v>0.1</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>10.1</v>
+        <v>2.2</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.6</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>14</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>14.4</v>
+        <v>19.4</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>91</v>
@@ -1987,7 +1989,7 @@
         <v>1.4</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>21.8</v>
+        <v>64.5</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>17.8</v>
@@ -2002,13 +2004,13 @@
         <v>8</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>16.9</v>
+        <v>18.2</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X18" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="X18" s="14" t="n">
+        <v>17</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>81.8</v>
@@ -2030,10 +2032,10 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>840.6</v>
-      </c>
-      <c r="D19" s="13" t="n">
-        <v>1.5</v>
+        <v>440.6</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>14</v>
@@ -2042,13 +2044,13 @@
         <v>19.5</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="H19" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>3.4</v>
@@ -2063,7 +2065,7 @@
         <v>1.4</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>11.5</v>
+        <v>46.4</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>92</v>
@@ -2072,7 +2074,7 @@
         <v>11.4</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>24.9</v>
+        <v>2.4</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>18.1</v>
@@ -2083,21 +2085,23 @@
       <c r="T19" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="U19" s="8" t="n">
+      <c r="U19" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V19" s="3" t="inlineStr"/>
+      <c r="V19" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="W19" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X19" s="8" t="n">
-        <v>18.8</v>
+        <v>4.9</v>
+      </c>
+      <c r="X19" s="14" t="n">
+        <v>185.3</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>81</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>27.4</v>
+        <v>127.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2115,23 +2119,23 @@
       <c r="C20" s="3" t="n">
         <v>153.1</v>
       </c>
-      <c r="D20" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="E20" s="3" t="n">
+      <c r="D20" s="11" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E20" s="11" t="n">
         <v>13.8</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>17.8</v>
+      <c r="F20" s="11" t="n">
+        <v>17.9</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>3.4</v>
@@ -2139,7 +2143,7 @@
       <c r="K20" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="L20" s="8" t="n">
+      <c r="L20" s="14" t="n">
         <v>19.4</v>
       </c>
       <c r="M20" s="3" t="n">
@@ -2155,10 +2159,10 @@
         <v>0.5</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>20.6</v>
+        <v>2</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>17.6</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>18.5</v>
@@ -2167,13 +2171,13 @@
         <v>76.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>5.7</v>
+        <v>14.4</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>16.8</v>
+        <v>75.5</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>18.6</v>
@@ -2206,32 +2210,32 @@
       <c r="E21" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="F21" s="13" t="n">
-        <v>1.8</v>
+      <c r="F21" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>11.9</v>
+        <v>7.2</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>16.4</v>
+      <c r="L21" s="14" t="n">
+        <v>56.2</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1</v>
+        <v>121.3</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>90.8</v>
@@ -2239,22 +2243,22 @@
       <c r="P21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q21" s="8" t="n">
-        <v>21.5</v>
+      <c r="Q21" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>18.9</v>
+        <v>43.1</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>74</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="V21" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="V21" s="14" t="n">
         <v>18.2</v>
       </c>
       <c r="W21" s="3" t="n">
@@ -2285,41 +2289,41 @@
       <c r="C22" s="3" t="n">
         <v>123.3</v>
       </c>
-      <c r="D22" s="13" t="n">
-        <v>12.06</v>
-      </c>
-      <c r="E22" s="13" t="n">
-        <v>94.40000000000001</v>
+      <c r="D22" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H22" s="8" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H22" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>11.6</v>
+      <c r="N22" s="14" t="n">
+        <v>68.90000000000001</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>1.8</v>
@@ -2330,17 +2334,17 @@
       <c r="R22" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="S22" s="8" t="n">
+      <c r="S22" s="14" t="n">
         <v>17.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>74</v>
+        <v>740.8</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>6.2</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>16.9</v>
@@ -2352,7 +2356,7 @@
         <v>94.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2368,43 +2372,43 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1921.2</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>11153.1</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>940.8</v>
+        <v>477.4</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>91</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>43.1</v>
+        <v>2654</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>69.8</v>
+        <v>636.4</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>80.8</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>38.2</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>16.1</v>
+        <v>161.4</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>122.1</v>
+        <v>14.6</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>816.4</v>
+        <v>31.6</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>1</v>
@@ -2416,7 +2420,7 @@
         <v>88.8</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>90</v>
+        <v>90.2</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>347.9</v>
@@ -2425,19 +2429,19 @@
         <v>40.6</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>918.9</v>
+        <v>919.8</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>911.8</v>
+        <v>942.1</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>48.4</v>
+        <v>148.8</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>113.8</v>
+        <v>13.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2468,7 +2472,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>69.8</v>
+        <v>636.4</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>1.5</v>
@@ -2480,13 +2484,13 @@
         <v>38.2</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>15.2</v>
+        <v>45.9</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>92.40000000000001</v>
@@ -2504,7 +2508,7 @@
         <v>18.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>69.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>8.1</v>
@@ -2512,11 +2516,11 @@
       <c r="V24" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="14" t="n">
         <v>16.8</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>87.09999999999999</v>
@@ -2538,40 +2542,40 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>490.4</v>
-      </c>
-      <c r="D25" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>13.6</v>
+        <v>130.4</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>64.31</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>15</v>
+        <v>18.8</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="H25" s="8" t="n">
-        <v>12.8</v>
+      <c r="H25" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="J25" s="8" t="n">
-        <v>18.1</v>
+      <c r="J25" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>849.2</v>
+        <v>15.1</v>
+      </c>
+      <c r="M25" s="14" t="n">
+        <v>34.2</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>15.4</v>
+        <v>1.1</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>910.8</v>
@@ -2579,17 +2583,17 @@
       <c r="P25" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="Q25" s="8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>11.6</v>
+      <c r="Q25" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="R25" s="14" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="S25" s="14" t="n">
+        <v>17.6</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>8</v>
@@ -2597,8 +2601,8 @@
       <c r="V25" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W25" s="8" t="n">
-        <v>12.9</v>
+      <c r="W25" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>18.1</v>
@@ -2623,7 +2627,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>287.8</v>
+        <v>87.8</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>23.4</v>
@@ -2638,19 +2642,19 @@
         <v>8.9</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="L26" s="8" t="n">
-        <v>84.59999999999999</v>
+        <v>5.9</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>14.9</v>
@@ -2662,10 +2666,10 @@
         <v>95</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0.8</v>
+        <v>11.4</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>28.7</v>
+        <v>20.7</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>17.3</v>
@@ -2680,19 +2684,19 @@
         <v>6.6</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>12.9</v>
+        <v>17.9</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X26" s="8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="X26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>88.5</v>
+        <v>2.5</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2708,16 +2712,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2305.9</v>
-      </c>
-      <c r="D27" s="11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D27" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="E27" s="11" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>18.8</v>
+      <c r="E27" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>9.1</v>
@@ -2726,22 +2730,22 @@
         <v>14.9</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>21.9</v>
+        <v>1.2</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="L27" s="8" t="n">
+      <c r="L27" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>94</v>
@@ -2755,11 +2759,11 @@
       <c r="R27" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="S27" s="8" t="n">
+      <c r="S27" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>5.6</v>
@@ -2768,7 +2772,7 @@
         <v>17.8</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>16.8</v>
+        <v>15.8</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>18.5</v>
@@ -2793,46 +2797,46 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2023.9</v>
-      </c>
-      <c r="D28" s="11" t="n">
+        <v>305.9</v>
+      </c>
+      <c r="D28" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="E28" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F28" s="11" t="n">
-        <v>17.9</v>
+      <c r="F28" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>22.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K28" s="8" t="n">
-        <v>65.40000000000001</v>
+        <v>1.1</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>14.7</v>
+        <v>15.4</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>95</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>18.8</v>
+        <v>0.8</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>20.5</v>
@@ -2847,7 +2851,7 @@
         <v>72.8</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>16.7</v>
@@ -2881,43 +2885,43 @@
         <v>289.8</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>21.4</v>
+        <v>21.9</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>13.3</v>
+        <v>13.8</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>17.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.1</v>
+        <v>84.5</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="L29" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="L29" s="14" t="n">
         <v>14.9</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>14.4</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>16.5</v>
+        <v>1.6</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>95</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>21.7</v>
@@ -2929,7 +2933,7 @@
         <v>18.2</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>70</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>7.8</v>
@@ -2963,15 +2967,15 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1682.9</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>1120.9</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F30" s="10" t="n">
+        <v>1689.9</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>1129.8</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="F30" s="9" t="n">
         <v>90.59999999999999</v>
       </c>
       <c r="G30" s="3" t="n">
@@ -2981,58 +2985,58 @@
         <v>80.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>9.1</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>456.6</v>
+        <v>38.6</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>71.8</v>
+        <v>1.6</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>20021.4</v>
+        <v>479.8</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>20.5</v>
+        <v>105.2</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>27.4</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>90.09999999999999</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>561.9</v>
+        <v>561.8</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>394.6</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>88</v>
+        <v>18.8</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>18.8</v>
+        <v>88</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>441.8</v>
+        <v>416.8</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>112.2</v>
+        <v>12.2</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3063,7 +3067,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>22.8</v>
+        <v>28.2</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>1.3</v>
@@ -3072,16 +3076,16 @@
         <v>1.8</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.1</v>
+        <v>38.6</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>14.3</v>
+        <v>1.4</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>16.8</v>
+        <v>16.1</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>94.09999999999999</v>
@@ -3099,10 +3103,10 @@
         <v>18.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v>16.3</v>
+        <v>116.3</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>6.2</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>17.6</v>
@@ -3114,10 +3118,10 @@
         <v>17.7</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>88.8</v>
+        <v>88.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>941.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3133,67 +3137,67 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>482.8</v>
-      </c>
-      <c r="D32" s="11" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="E32" s="13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>11.9</v>
+        <v>481.8</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F32" s="15" t="n">
+        <v>71.90000000000001</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>12.3</v>
+        <v>12.9</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>14.9</v>
+        <v>16.1</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>105.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>16.8</v>
+        <v>16.1</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>895</v>
+        <v>83</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="R32" s="8" t="n">
-        <v>19.8</v>
+        <v>17</v>
+      </c>
+      <c r="R32" s="14" t="n">
+        <v>15.8</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>901.1</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="W32" s="8" t="n">
-        <v>16.6</v>
+        <v>15.9</v>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>15.6</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>17.7</v>
@@ -3218,46 +3222,46 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>482.8</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F33" s="13" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="G33" s="8" t="n">
-        <v>11.7</v>
+        <v>422.8</v>
+      </c>
+      <c r="D33" s="15" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>6618.45</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <v>91.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>20.6</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>4.9</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>12.3</v>
+        <v>12.9</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>1.2</v>
+        <v>16.1</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="N33" s="3" t="n">
-        <v>15.8</v>
+      <c r="N33" s="14" t="n">
+        <v>92.40000000000001</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>93</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>23.8</v>
@@ -3266,25 +3270,25 @@
         <v>16.8</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="U33" s="8" t="n">
+        <v>319.5</v>
+      </c>
+      <c r="U33" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="W33" s="8" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="X33" s="8" t="n">
-        <v>40.6</v>
+      <c r="W33" s="14" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>71.8</v>
+        <v>71</v>
       </c>
       <c r="Z33" s="3" t="n">
         <v>4.8</v>
@@ -3305,56 +3309,56 @@
       <c r="C34" s="3" t="n">
         <v>492.8</v>
       </c>
-      <c r="D34" s="8" t="n">
+      <c r="D34" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="E34" s="13" t="n">
-        <v>11.36</v>
+      <c r="E34" s="15" t="n">
+        <v>3.6</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="H34" s="8" t="n">
-        <v>8.300000000000001</v>
+      <c r="H34" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>23.1</v>
+        <v>2.3</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M34" s="8" t="n">
-        <v>11.6</v>
+      <c r="M34" s="14" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>1.1</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>17.7</v>
+        <v>1.7</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>26.8</v>
+        <v>56.8</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>12.8</v>
@@ -3363,16 +3367,14 @@
         <v>18</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X34" s="8" t="n">
-        <v>16.7</v>
-      </c>
+        <v>15.8</v>
+      </c>
+      <c r="X34" s="3" t="inlineStr"/>
       <c r="Y34" s="3" t="n">
         <v>21</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>89.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3388,18 +3390,18 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="E35" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="E35" s="14" t="n">
         <v>13.6</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="G35" s="8" t="n">
+      <c r="F35" s="15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G35" s="14" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -3412,45 +3414,45 @@
         <v>4</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="M35" s="8" t="n">
-        <v>13.5</v>
+      <c r="M35" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.7</v>
+        <v>17.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>9180</v>
+        <v>90</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q35" s="8" t="n">
-        <v>18.8</v>
+        <v>2</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>18.9</v>
+        <v>18.2</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>600.8</v>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v>1424.8</v>
+        <v>60</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X35" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X35" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="Y35" s="3" t="n">
@@ -3481,17 +3483,17 @@
       <c r="E36" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="G36" s="8" t="n">
+      <c r="F36" s="15" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="G36" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>4</v>
@@ -3505,8 +3507,8 @@
       <c r="M36" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>18.9</v>
+      <c r="N36" s="14" t="n">
+        <v>81.09999999999999</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>91</v>
@@ -3514,20 +3516,20 @@
       <c r="P36" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q36" s="8" t="n">
-        <v>124.2</v>
+      <c r="Q36" s="3" t="n">
+        <v>29.2</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="S36" s="8" t="n">
-        <v>71</v>
+      <c r="S36" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>552.1</v>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v>1424.8</v>
+        <v>55.1</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>18.4</v>
@@ -3558,76 +3560,76 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>122.8</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>124.2</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>825.8</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>22.6</v>
+        <v>128.1</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>92.59999999999999</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>22.9</v>
+        <v>22</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>4</v>
+        <v>18.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>110.8</v>
+        <v>110.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>18.6</v>
+        <v>12.6</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>122.9</v>
+        <v>121.8</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>29.1</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>8012</v>
+        <v>15.6</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>19.1</v>
+        <v>11.1</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>449</v>
+        <v>44930.3</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>113.4</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>84.8</v>
+        <v>24.8</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>313.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>25.8</v>
+        <v>24.8</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>82</v>
+        <v>83.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>940.2</v>
+        <v>41252.4</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>128.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3643,7 +3645,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>9438.6</v>
+        <v>438.6</v>
       </c>
       <c r="D38" s="11" t="n">
         <v>23.8</v>
@@ -3655,34 +3657,34 @@
         <v>18</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>12.3</v>
+        <v>22.3</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>12.1</v>
+        <v>2.1</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="K38" s="8" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="L38" s="8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L38" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="N38" s="8" t="n">
-        <v>52.1</v>
+      <c r="N38" s="14" t="n">
+        <v>58.1</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>89.8</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>22.7</v>
@@ -3691,10 +3693,10 @@
         <v>17.4</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>17</v>
+        <v>480.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>62.1</v>
+        <v>63.9</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>11</v>
@@ -3703,16 +3705,16 @@
         <v>18.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>16.1</v>
+        <v>15.1</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>224.9</v>
+        <v>21.9</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3728,40 +3730,40 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>395</v>
-      </c>
-      <c r="D39" s="13" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="E39" s="13" t="n">
-        <v>92</v>
+        <v>2392.3</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>23</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="G39" s="8" t="n">
-        <v>11.8</v>
+      <c r="G39" s="14" t="n">
+        <v>11.9</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>5.2</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>8.5</v>
+        <v>15.9</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="N39" s="8" t="n">
-        <v>52.1</v>
+        <v>1.8</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N39" s="14" t="n">
+        <v>1.5</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
@@ -3769,35 +3771,35 @@
       <c r="P39" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q39" s="8" t="n">
-        <v>19.6</v>
+      <c r="Q39" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>52.8</v>
+        <v>52</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v>71</v>
+        <v>14</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>1.9</v>
+        <v>12.1</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>11.8</v>
+        <v>71</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>16.4</v>
+        <v>6.9</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3815,42 +3817,40 @@
       <c r="C40" s="3" t="n">
         <v>2942.1</v>
       </c>
-      <c r="D40" s="8" t="n">
-        <v>18.8</v>
+      <c r="D40" s="15" t="n">
+        <v>49.2</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>19.1</v>
+        <v>13.8</v>
+      </c>
+      <c r="F40" s="15" t="n">
+        <v>4.9</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="I40" s="8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J40" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr"/>
+      <c r="L40" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="M40" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="P40" s="3" t="n">
         <v>2.2</v>
-      </c>
-      <c r="K40" s="3" t="inlineStr"/>
-      <c r="L40" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="O40" s="3" t="n">
-        <v>299.5</v>
-      </c>
-      <c r="P40" s="3" t="n">
-        <v>25.5</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>23.8</v>
@@ -3862,7 +3862,7 @@
         <v>17.2</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>68.5</v>
+        <v>58.8</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>12</v>
@@ -3871,7 +3871,7 @@
         <v>19.4</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>16</v>
+        <v>12.1</v>
       </c>
       <c r="X40" s="3" t="n">
         <v>16.8</v>
@@ -3907,14 +3907,14 @@
       <c r="F41" s="11" t="n">
         <v>13.1</v>
       </c>
-      <c r="G41" s="8" t="n">
-        <v>11.1</v>
+      <c r="G41" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="I41" s="8" t="n">
-        <v>11.1</v>
+      <c r="I41" s="14" t="n">
+        <v>81</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>4.7</v>
@@ -3926,35 +3926,35 @@
         <v>14.8</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>13.6</v>
+        <v>1.3</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" s="8" t="n">
-        <v>123.9</v>
+      <c r="Q41" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>14.5</v>
+        <v>1.5</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>162.5</v>
+        <v>62.5</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="W41" s="8" t="n">
-        <v>72</v>
+        <v>19</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>18.2</v>
@@ -3963,7 +3963,7 @@
         <v>83</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3979,22 +3979,24 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>349.1</v>
-      </c>
-      <c r="D42" s="8" t="n">
+        <v>340.1</v>
+      </c>
+      <c r="D42" s="11" t="n">
         <v>22.4</v>
       </c>
-      <c r="E42" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F42" s="13" t="n">
-        <v>1.8</v>
+      <c r="E42" s="11" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>18.5</v>
       </c>
       <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="8" t="n">
+      <c r="H42" s="3" t="n">
         <v>13.7</v>
       </c>
-      <c r="I42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="J42" s="3" t="n">
         <v>4</v>
       </c>
@@ -4002,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>11.4</v>
+        <v>14.6</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>14.6</v>
@@ -4017,16 +4019,16 @@
         <v>2</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>43.4</v>
+        <v>18</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>16</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>1460.5</v>
+        <v>60.5</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>10.4</v>
@@ -4058,41 +4060,41 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>517</v>
-      </c>
-      <c r="D43" s="13" t="n">
-        <v>0.1</v>
+        <v>537</v>
+      </c>
+      <c r="D43" s="15" t="n">
+        <v>49.5</v>
       </c>
       <c r="E43" s="12" t="inlineStr"/>
       <c r="F43" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="G43" s="8" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>11.4</v>
+      <c r="G43" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>11.7</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>19.7</v>
+        <v>1.4</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>21.1</v>
+        <v>8</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>4.4</v>
+        <v>15.1</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>16.9</v>
+        <v>1.6</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>2</v>
@@ -4100,23 +4102,23 @@
       <c r="Q43" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R43" s="8" t="n">
-        <v>16.5</v>
+      <c r="R43" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>0.2</v>
+        <v>11.2</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>16.2</v>
@@ -4141,7 +4143,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>653.1</v>
+        <v>223.1</v>
       </c>
       <c r="D44" s="11" t="n">
         <v>23.4</v>
@@ -4166,7 +4168,7 @@
         <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>13.6</v>
+        <v>15.1</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>12.6</v>
@@ -4176,13 +4178,13 @@
         <v>91</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R44" s="8" t="n">
-        <v>68.09999999999999</v>
+      <c r="R44" s="14" t="n">
+        <v>67.09999999999999</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>13.9</v>
@@ -4191,7 +4193,7 @@
         <v>59.5</v>
       </c>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="n">
+      <c r="V44" s="14" t="n">
         <v>18.1</v>
       </c>
       <c r="W44" s="3" t="inlineStr"/>
@@ -4212,76 +4214,76 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2283</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>198.5</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>110.2</v>
+        <v>2282</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>1981.8</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>110.8</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>128.8</v>
+        <v>20.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>13.2</v>
+        <v>15.2</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>26.2</v>
+        <v>286.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>10.1</v>
+        <v>180.1</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>82.5</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>91.8</v>
+        <v>31.3</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>290.9</v>
+        <v>240.9</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>112.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>121.6</v>
+        <v>21</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>104.1</v>
+        <v>10.4</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>99.8</v>
+        <v>92.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>381</v>
+        <v>331</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>111.8</v>
+        <v>119.8</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>220.8</v>
+        <v>22</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>36</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>4648.4</v>
+        <v>966.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>28.1</v>
+        <v>28.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4297,16 +4299,16 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>13.2</v>
+        <v>12.3</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>10.3</v>
@@ -4320,23 +4322,21 @@
       <c r="J46" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>4.6</v>
-      </c>
+      <c r="K46" s="3" t="inlineStr"/>
       <c r="L46" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="M46" s="8" t="n">
+      <c r="M46" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="N46" s="8" t="n">
-        <v>38.9</v>
+      <c r="N46" s="3" t="n">
+        <v>6.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>254.1</v>
+        <v>20.4</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>22.8</v>
@@ -4350,20 +4350,18 @@
       <c r="T46" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="U46" s="8" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U46" s="3" t="inlineStr"/>
       <c r="V46" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="W46" s="8" t="n">
+      <c r="W46" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="X46" s="8" t="n">
+      <c r="X46" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>87.8</v>
+        <v>77.8</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>4.8</v>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_correct_values.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_correct_values.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -161,13 +161,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -825,7 +822,7 @@
       <c r="Q4" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="11" t="n">
         <v>17.9</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -835,10 +832,10 @@
         <v>52</v>
       </c>
       <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="3" t="n">
-        <v>107.1</v>
-      </c>
-      <c r="W4" s="3" t="n">
+      <c r="V4" s="13" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="W4" s="13" t="n">
         <v>1.6</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
@@ -902,7 +899,7 @@
       <c r="Q5" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="11" t="n">
         <v>17.2</v>
       </c>
       <c r="S5" s="14" t="n">
@@ -987,7 +984,7 @@
       <c r="Q6" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="11" t="n">
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -1067,8 +1064,8 @@
       <c r="P7" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="n">
+      <c r="Q7" s="12" t="inlineStr"/>
+      <c r="R7" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1153,7 +1150,7 @@
       <c r="Q8" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="11" t="n">
         <v>17.5</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1209,13 +1206,13 @@
       <c r="J9" s="3" t="n">
         <v>260.5</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="9" t="n">
         <v>51.1</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="9" t="n">
         <v>73.40000000000001</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="9" t="n">
         <v>68.90000000000001</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1227,10 +1224,10 @@
       <c r="P9" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="9" t="n">
         <v>114</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="11" t="n">
         <v>88.09999999999999</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1242,10 +1239,10 @@
       <c r="U9" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="9" t="n">
         <v>94</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="9" t="n">
         <v>80.8</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1297,10 +1294,10 @@
       <c r="K10" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="9" t="n">
         <v>14.7</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="9" t="n">
         <v>13.8</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1312,10 +1309,10 @@
       <c r="P10" s="3" t="n">
         <v>113.8</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="S10" s="14" t="n">
@@ -1327,10 +1324,10 @@
       <c r="U10" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="9" t="n">
         <v>18.8</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="9" t="n">
         <v>16.8</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1382,7 +1379,7 @@
       <c r="K11" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="13" t="n">
         <v>1.2</v>
       </c>
       <c r="M11" s="3" t="n">
@@ -1415,7 +1412,7 @@
       <c r="V11" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="11" t="n">
         <v>16.8</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1495,10 +1492,10 @@
       <c r="U12" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="13" t="n">
         <v>1.6</v>
       </c>
-      <c r="W12" s="3" t="n">
+      <c r="W12" s="11" t="n">
         <v>14.8</v>
       </c>
       <c r="X12" s="3" t="n">
@@ -1583,7 +1580,7 @@
       <c r="V13" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="11" t="n">
         <v>15.8</v>
       </c>
       <c r="X13" s="3" t="n">
@@ -1650,7 +1647,7 @@
       <c r="P14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="13" t="n">
         <v>2.8</v>
       </c>
       <c r="R14" s="3" t="n">
@@ -1668,7 +1665,7 @@
       <c r="V14" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="11" t="n">
         <v>14.8</v>
       </c>
       <c r="X14" s="3" t="n">
@@ -1751,7 +1748,7 @@
       <c r="V15" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="11" t="n">
         <v>15.7</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1800,13 +1797,13 @@
       <c r="J16" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="9" t="n">
         <v>46</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="9" t="n">
         <v>73.2</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="9" t="n">
         <v>69.40000000000001</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1818,10 +1815,10 @@
       <c r="P16" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="9" t="n">
         <v>6.9</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="9" t="n">
         <v>61.4</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1833,10 +1830,10 @@
       <c r="U16" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="9" t="n">
         <v>18.6</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1870,7 +1867,7 @@
       <c r="E17" s="9" t="n">
         <v>13.8</v>
       </c>
-      <c r="F17" s="15" t="n">
+      <c r="F17" s="13" t="n">
         <v>4.8</v>
       </c>
       <c r="G17" s="3" t="n">
@@ -1888,10 +1885,10 @@
       <c r="K17" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="9" t="n">
         <v>14.6</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="9" t="n">
         <v>13.9</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1903,10 +1900,10 @@
       <c r="P17" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" s="9" t="n">
         <v>16.7</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1918,10 +1915,10 @@
       <c r="U17" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="9" t="n">
         <v>16.9</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="11" t="n">
         <v>15.7</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1970,7 +1967,7 @@
       <c r="J18" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
@@ -1988,7 +1985,7 @@
       <c r="P18" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q18" s="3" t="n">
+      <c r="Q18" s="13" t="n">
         <v>64.5</v>
       </c>
       <c r="R18" s="3" t="n">
@@ -2055,13 +2052,13 @@
       <c r="J19" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="11" t="n">
         <v>18.7</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="13" t="n">
         <v>1.4</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2073,7 +2070,7 @@
       <c r="P19" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="Q19" s="3" t="n">
+      <c r="Q19" s="13" t="n">
         <v>2.4</v>
       </c>
       <c r="R19" s="3" t="n">
@@ -2091,7 +2088,7 @@
       <c r="V19" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="W19" s="3" t="n">
+      <c r="W19" s="13" t="n">
         <v>4.9</v>
       </c>
       <c r="X19" s="14" t="n">
@@ -2140,7 +2137,7 @@
       <c r="J20" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="11" t="n">
         <v>5.6</v>
       </c>
       <c r="L20" s="14" t="n">
@@ -2158,10 +2155,10 @@
       <c r="P20" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="R20" s="3" t="n">
+      <c r="R20" s="13" t="n">
         <v>87.59999999999999</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2176,7 +2173,7 @@
       <c r="V20" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="W20" s="3" t="n">
+      <c r="W20" s="13" t="n">
         <v>75.5</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2225,10 +2222,10 @@
       <c r="J21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="11" t="n">
         <v>10.9</v>
       </c>
-      <c r="L21" s="14" t="n">
+      <c r="L21" s="13" t="n">
         <v>56.2</v>
       </c>
       <c r="M21" s="3" t="n">
@@ -2310,7 +2307,7 @@
       <c r="J22" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="11" t="n">
         <v>3</v>
       </c>
       <c r="L22" s="3" t="n">
@@ -2395,13 +2392,13 @@
       <c r="J23" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="11" t="n">
         <v>38.2</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="9" t="n">
         <v>161.4</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="9" t="n">
         <v>14.6</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2413,10 +2410,10 @@
       <c r="P23" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="9" t="n">
         <v>109</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="9" t="n">
         <v>88.8</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2428,10 +2425,10 @@
       <c r="U23" s="3" t="n">
         <v>40.6</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="9" t="n">
         <v>919.8</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="9" t="n">
         <v>83.90000000000001</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2483,10 +2480,10 @@
       <c r="K24" s="3" t="n">
         <v>38.2</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="9" t="n">
         <v>45.9</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="9" t="n">
         <v>14.4</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2498,10 +2495,10 @@
       <c r="P24" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="9" t="n">
         <v>21.8</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="9" t="n">
         <v>47.8</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2513,10 +2510,10 @@
       <c r="U24" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="9" t="n">
         <v>18.3</v>
       </c>
-      <c r="W24" s="14" t="n">
+      <c r="W24" s="9" t="n">
         <v>16.8</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2547,7 +2544,7 @@
       <c r="D25" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="E25" s="15" t="n">
+      <c r="E25" s="13" t="n">
         <v>64.31</v>
       </c>
       <c r="F25" s="3" t="n">
@@ -2568,7 +2565,7 @@
       <c r="K25" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="11" t="n">
         <v>15.1</v>
       </c>
       <c r="M25" s="14" t="n">
@@ -2583,10 +2580,10 @@
       <c r="P25" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="Q25" s="3" t="n">
+      <c r="Q25" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="R25" s="14" t="n">
+      <c r="R25" s="13" t="n">
         <v>72.90000000000001</v>
       </c>
       <c r="S25" s="14" t="n">
@@ -2598,10 +2595,10 @@
       <c r="U25" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="V25" s="3" t="n">
+      <c r="V25" s="11" t="n">
         <v>16.6</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="W25" s="11" t="n">
         <v>15.9</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2653,7 +2650,7 @@
       <c r="K26" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="11" t="n">
         <v>14.6</v>
       </c>
       <c r="M26" s="3" t="n">
@@ -2668,7 +2665,7 @@
       <c r="P26" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="11" t="n">
         <v>20.7</v>
       </c>
       <c r="R26" s="3" t="n">
@@ -2683,10 +2680,10 @@
       <c r="U26" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="11" t="n">
         <v>17.9</v>
       </c>
-      <c r="W26" s="3" t="n">
+      <c r="W26" s="11" t="n">
         <v>16.5</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2738,7 +2735,7 @@
       <c r="K27" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="L27" s="11" t="n">
         <v>15.4</v>
       </c>
       <c r="M27" s="3" t="n">
@@ -2753,7 +2750,7 @@
       <c r="P27" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" s="11" t="n">
         <v>20.8</v>
       </c>
       <c r="R27" s="3" t="n">
@@ -2768,10 +2765,10 @@
       <c r="U27" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="V27" s="3" t="n">
+      <c r="V27" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="W27" s="3" t="n">
+      <c r="W27" s="11" t="n">
         <v>15.8</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2823,7 +2820,7 @@
       <c r="K28" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" s="11" t="n">
         <v>15.4</v>
       </c>
       <c r="M28" s="3" t="n">
@@ -2838,7 +2835,7 @@
       <c r="P28" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" s="11" t="n">
         <v>20.5</v>
       </c>
       <c r="R28" s="3" t="n">
@@ -2853,10 +2850,10 @@
       <c r="U28" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V28" s="3" t="n">
+      <c r="V28" s="11" t="n">
         <v>16.7</v>
       </c>
-      <c r="W28" s="3" t="n">
+      <c r="W28" s="11" t="n">
         <v>14.8</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2908,10 +2905,10 @@
       <c r="K29" s="3" t="n">
         <v>6.7</v>
       </c>
-      <c r="L29" s="14" t="n">
+      <c r="L29" s="11" t="n">
         <v>14.9</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="13" t="n">
         <v>84.40000000000001</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2923,7 +2920,7 @@
       <c r="P29" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" s="11" t="n">
         <v>21.7</v>
       </c>
       <c r="R29" s="3" t="n">
@@ -2938,10 +2935,10 @@
       <c r="U29" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="V29" s="11" t="n">
         <v>18.8</v>
       </c>
-      <c r="W29" s="3" t="n">
+      <c r="W29" s="11" t="n">
         <v>17.1</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2990,13 +2987,13 @@
       <c r="J30" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="9" t="n">
         <v>38.6</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="9" t="n">
         <v>19.1</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="9" t="n">
         <v>11.7</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3008,10 +3005,10 @@
       <c r="P30" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="9" t="n">
         <v>105.2</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="9" t="n">
         <v>27.4</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3023,10 +3020,10 @@
       <c r="U30" s="3" t="n">
         <v>394.6</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="9" t="n">
         <v>18.8</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="9" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3078,10 +3075,10 @@
       <c r="K31" s="3" t="n">
         <v>38.6</v>
       </c>
-      <c r="L31" s="3" t="n">
+      <c r="L31" s="11" t="n">
         <v>14.9</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="9" t="n">
         <v>1.4</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3093,10 +3090,10 @@
       <c r="P31" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="9" t="n">
         <v>17.5</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3108,10 +3105,10 @@
       <c r="U31" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="V31" s="11" t="n">
         <v>17.6</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="11" t="n">
         <v>16.2</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3145,7 +3142,7 @@
       <c r="E32" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="F32" s="15" t="n">
+      <c r="F32" s="13" t="n">
         <v>71.90000000000001</v>
       </c>
       <c r="G32" s="3" t="n">
@@ -3166,8 +3163,8 @@
       <c r="L32" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="M32" s="3" t="n">
-        <v>105.1</v>
+      <c r="M32" s="13" t="n">
+        <v>10.51</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>16.1</v>
@@ -3193,7 +3190,7 @@
       <c r="U32" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="V32" s="3" t="n">
+      <c r="V32" s="11" t="n">
         <v>15.9</v>
       </c>
       <c r="W32" s="3" t="n">
@@ -3224,10 +3221,10 @@
       <c r="C33" s="3" t="n">
         <v>422.8</v>
       </c>
-      <c r="D33" s="15" t="n">
+      <c r="D33" s="13" t="n">
         <v>49.1</v>
       </c>
-      <c r="E33" s="15" t="n">
+      <c r="E33" s="13" t="n">
         <v>6618.45</v>
       </c>
       <c r="F33" s="3" t="n">
@@ -3278,7 +3275,7 @@
       <c r="U33" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V33" s="3" t="n">
+      <c r="V33" s="11" t="n">
         <v>18</v>
       </c>
       <c r="W33" s="14" t="n">
@@ -3312,7 +3309,7 @@
       <c r="D34" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="E34" s="15" t="n">
+      <c r="E34" s="13" t="n">
         <v>3.6</v>
       </c>
       <c r="F34" s="3" t="n">
@@ -3336,7 +3333,7 @@
       <c r="L34" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M34" s="14" t="n">
+      <c r="M34" s="13" t="n">
         <v>91.59999999999999</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3351,7 +3348,7 @@
       <c r="Q34" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="13" t="n">
         <v>1.7</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3363,7 +3360,7 @@
       <c r="U34" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="V34" s="11" t="n">
         <v>18</v>
       </c>
       <c r="W34" s="3" t="n">
@@ -3398,7 +3395,7 @@
       <c r="E35" s="14" t="n">
         <v>13.6</v>
       </c>
-      <c r="F35" s="15" t="n">
+      <c r="F35" s="13" t="n">
         <v>4.4</v>
       </c>
       <c r="G35" s="14" t="n">
@@ -3446,10 +3443,10 @@
       <c r="U35" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="V35" s="11" t="n">
         <v>20.7</v>
       </c>
-      <c r="W35" s="3" t="n">
+      <c r="W35" s="13" t="n">
         <v>1.7</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3483,7 +3480,7 @@
       <c r="E36" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="F36" s="15" t="n">
+      <c r="F36" s="13" t="n">
         <v>92.09999999999999</v>
       </c>
       <c r="G36" s="3" t="n">
@@ -3531,7 +3528,7 @@
       <c r="U36" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="V36" s="11" t="n">
         <v>18.4</v>
       </c>
       <c r="W36" s="3" t="n">
@@ -3583,13 +3580,13 @@
       <c r="J37" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="9" t="n">
         <v>121.8</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="9" t="n">
         <v>83.09999999999999</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="9" t="n">
         <v>15.6</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3601,10 +3598,10 @@
       <c r="P37" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="9" t="n">
         <v>113.4</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="9" t="n">
         <v>81</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3616,10 +3613,10 @@
       <c r="U37" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="11" t="n">
         <v>91</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="9" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3671,10 +3668,10 @@
       <c r="K38" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="9" t="n">
         <v>15.1</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="9" t="n">
         <v>14</v>
       </c>
       <c r="N38" s="14" t="n">
@@ -3686,10 +3683,10 @@
       <c r="P38" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="9" t="n">
         <v>17.4</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3701,10 +3698,10 @@
       <c r="U38" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="11" t="n">
         <v>18.2</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="9" t="n">
         <v>15.1</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3756,7 +3753,7 @@
       <c r="K39" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="L39" s="3" t="n">
+      <c r="L39" s="13" t="n">
         <v>1.8</v>
       </c>
       <c r="M39" s="3" t="n">
@@ -3786,7 +3783,7 @@
       <c r="U39" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="13" t="n">
         <v>1.9</v>
       </c>
       <c r="W39" s="3" t="n">
@@ -3817,13 +3814,13 @@
       <c r="C40" s="3" t="n">
         <v>2942.1</v>
       </c>
-      <c r="D40" s="15" t="n">
+      <c r="D40" s="13" t="n">
         <v>49.2</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F40" s="15" t="n">
+      <c r="F40" s="13" t="n">
         <v>4.9</v>
       </c>
       <c r="G40" s="3" t="n">
@@ -3836,7 +3833,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="3" t="inlineStr"/>
+      <c r="K40" s="12" t="inlineStr"/>
       <c r="L40" s="3" t="n">
         <v>16</v>
       </c>
@@ -3925,7 +3922,7 @@
       <c r="L41" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="13" t="n">
         <v>1.3</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
@@ -3935,10 +3932,10 @@
       <c r="P41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="13" t="n">
         <v>1.8</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="13" t="n">
         <v>1.5</v>
       </c>
       <c r="S41" s="3" t="n">
@@ -4006,7 +4003,7 @@
       <c r="L42" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="M42" s="3" t="n">
+      <c r="M42" s="13" t="n">
         <v>1.3</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -4021,7 +4018,7 @@
       <c r="Q42" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="13" t="n">
         <v>4.8</v>
       </c>
       <c r="S42" s="3" t="n">
@@ -4062,7 +4059,7 @@
       <c r="C43" s="3" t="n">
         <v>537</v>
       </c>
-      <c r="D43" s="15" t="n">
+      <c r="D43" s="13" t="n">
         <v>49.5</v>
       </c>
       <c r="E43" s="12" t="inlineStr"/>
@@ -4102,7 +4099,7 @@
       <c r="Q43" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="13" t="n">
         <v>1.6</v>
       </c>
       <c r="S43" s="3" t="n">
@@ -4117,7 +4114,7 @@
       <c r="V43" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="W43" s="3" t="n">
+      <c r="W43" s="13" t="n">
         <v>0.1</v>
       </c>
       <c r="X43" s="3" t="n">
@@ -4183,7 +4180,7 @@
       <c r="Q44" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R44" s="14" t="n">
+      <c r="R44" s="13" t="n">
         <v>67.09999999999999</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4196,7 +4193,7 @@
       <c r="V44" s="14" t="n">
         <v>18.1</v>
       </c>
-      <c r="W44" s="3" t="inlineStr"/>
+      <c r="W44" s="12" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4237,13 +4234,13 @@
       <c r="J45" s="3" t="n">
         <v>286.2</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="9" t="n">
         <v>180.1</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="9" t="n">
         <v>89.90000000000001</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" s="9" t="n">
         <v>7</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4255,10 +4252,10 @@
       <c r="P45" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="9" t="n">
         <v>10.4</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4270,10 +4267,10 @@
       <c r="U45" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="9" t="n">
         <v>119.8</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="9" t="n">
         <v>22</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4323,10 +4320,10 @@
         <v>4.4</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="n">
+      <c r="L46" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="9" t="n">
         <v>13.8</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4338,10 +4335,10 @@
       <c r="P46" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" s="9" t="n">
         <v>22.8</v>
       </c>
-      <c r="R46" s="3" t="n">
+      <c r="R46" s="9" t="n">
         <v>17.1</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4351,10 +4348,10 @@
         <v>58.5</v>
       </c>
       <c r="U46" s="3" t="inlineStr"/>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="9" t="n">
         <v>15.9</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_correct_values.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_correct_values.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -41,8 +41,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -53,14 +65,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,10 +152,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -158,13 +167,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -778,16 +787,16 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>582.2</v>
+        <v>58.5</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>25</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>11.5</v>
@@ -799,19 +808,19 @@
         <v>2.8</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="M4" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M4" s="11" t="n">
         <v>13.1</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>1.4</v>
+      <c r="N4" s="8" t="n">
+        <v>29.5</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>87</v>
@@ -819,25 +828,25 @@
       <c r="P4" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="R4" s="11" t="n">
+      <c r="R4" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="13" t="n">
-        <v>10.71</v>
-      </c>
-      <c r="W4" s="13" t="n">
-        <v>1.6</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="W4" s="11" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
@@ -855,7 +864,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>388.5</v>
+        <v>38.8</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>24</v>
@@ -869,59 +878,59 @@
       <c r="G5" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>12.1</v>
+      <c r="H5" s="8" t="n">
+        <v>12.8</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="M5" s="3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="L5" s="15" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="M5" s="11" t="n">
         <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>18.9</v>
+        <v>12.1</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>92</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Q5" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="Q5" s="11" t="n">
         <v>22.4</v>
       </c>
-      <c r="R5" s="11" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="S5" s="14" t="n">
-        <v>16.7</v>
+      <c r="R5" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>52</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>15.2</v>
+        <v>1.5</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>7.5</v>
+        <v>75.5</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>6</v>
@@ -940,22 +949,22 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>508.9</v>
+        <v>50.8</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>18.5</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>12.8</v>
+        <v>13.9</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>2.4</v>
@@ -964,34 +973,34 @@
         <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="M6" s="14" t="n">
-        <v>30.9</v>
+      <c r="M6" s="11" t="n">
+        <v>13.1</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>19.5</v>
+        <v>45.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>92</v>
+        <v>1.1</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="11" t="n">
         <v>23.6</v>
       </c>
-      <c r="R6" s="11" t="n">
+      <c r="R6" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>61.9</v>
+        <v>61.5</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>10.4</v>
@@ -999,17 +1008,17 @@
       <c r="V6" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="11" t="n">
         <v>16.8</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1027,49 +1036,53 @@
       <c r="C7" s="3" t="n">
         <v>512.9</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="11" t="n">
         <v>23.9</v>
       </c>
-      <c r="E7" s="11" t="inlineStr"/>
-      <c r="F7" s="3" t="n">
-        <v>18</v>
+      <c r="E7" s="11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>18.5</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="H7" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>11.4</v>
+        <v>2.4</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="11" t="n">
         <v>13.6</v>
       </c>
-      <c r="N7" s="14" t="n">
-        <v>52.1</v>
+      <c r="N7" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>293</v>
+        <v>52.4</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Q7" s="12" t="inlineStr"/>
-      <c r="R7" s="11" t="n">
-        <v>17.6</v>
+        <v>1</v>
+      </c>
+      <c r="Q7" s="11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R7" s="15" t="n">
+        <v>1.7</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>17.9</v>
+        <v>12.4</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>59.1</v>
@@ -1077,20 +1090,20 @@
       <c r="U7" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="V7" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="W7" s="3" t="n">
+      <c r="V7" s="15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W7" s="11" t="n">
         <v>16.6</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>82.2</v>
+        <v>82.5</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>21</v>
+        <v>0.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1112,10 +1125,10 @@
         <v>21.6</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>17.9</v>
+        <v>17.6</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>7.7</v>
@@ -1124,53 +1137,59 @@
         <v>12.9</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>6.4</v>
+        <v>11.9</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="M8" s="3" t="n">
-        <v>14.2</v>
+      <c r="M8" s="11" t="n">
+        <v>14.1</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>16.2</v>
+        <v>40.3</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>93</v>
+        <v>11.6</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="11" t="n">
         <v>20.5</v>
       </c>
-      <c r="R8" s="11" t="n">
+      <c r="R8" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>18.1</v>
+        <v>1.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="W8" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="W8" s="11" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="X8" s="3" t="inlineStr"/>
-      <c r="Y8" s="3" t="inlineStr"/>
-      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1185,75 +1204,75 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2224.9</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>118.5</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="F9" s="9" t="n">
+        <v>222.4</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>1118.5</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="F9" s="10" t="n">
         <v>93.09999999999999</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>20.9</v>
+        <v>30.9</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>63.1</v>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="n">
+        <v>706.4</v>
+      </c>
       <c r="J9" s="3" t="n">
-        <v>260.5</v>
-      </c>
-      <c r="K9" s="9" t="n">
+        <v>260.4</v>
+      </c>
+      <c r="K9" s="10" t="n">
         <v>51.1</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" s="10" t="n">
         <v>73.40000000000001</v>
       </c>
-      <c r="M9" s="9" t="n">
-        <v>68.90000000000001</v>
+      <c r="M9" s="10" t="n">
+        <v>0.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>16.6</v>
+        <v>166.4</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1590.1</v>
+        <v>59</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="Q9" s="11" t="n">
         <v>114</v>
       </c>
-      <c r="R9" s="11" t="n">
+      <c r="R9" s="10" t="n">
         <v>88.09999999999999</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>86.8</v>
+        <v>86.2</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>212.6</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="V9" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="V9" s="10" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="W9" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>117.8</v>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="W9" s="9" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>848.1</v>
-      </c>
-      <c r="Z9" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="Z9" s="3" t="inlineStr"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1268,7 +1287,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>495</v>
+        <v>44.5</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>23.7</v>
@@ -1286,58 +1305,56 @@
         <v>12.6</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.2</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L10" s="9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="10" t="n">
         <v>14.7</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="11" t="n">
         <v>13.8</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>921.8</v>
+        <v>99.8</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>113.8</v>
-      </c>
-      <c r="Q10" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="R10" s="11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q10" s="11" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="R10" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="S10" s="14" t="n">
-        <v>78.2</v>
+      <c r="S10" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>62.8</v>
+        <v>19.6</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" s="11" t="n">
         <v>16.8</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="Y10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z10" s="3" t="n">
         <v>83</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>3.8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1353,7 +1370,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>924.2</v>
+        <v>191.8</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>22.5</v>
@@ -1365,63 +1382,65 @@
         <v>18.1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>28.8</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>12.6</v>
+        <v>14.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L11" s="13" t="n">
-        <v>1.2</v>
+        <v>10</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>14.8</v>
+        <v>14</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>18.1</v>
+        <v>11.9</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>885</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>20.8</v>
+        <v>6.4</v>
+      </c>
+      <c r="Q11" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="R11" s="15" t="n">
+        <v>1.1</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>82</v>
+        <v>140649.1</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>10.6</v>
+        <v>55.1</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="W11" s="11" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>17.9</v>
+        <v>34.1</v>
+      </c>
+      <c r="W11" s="15" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="X11" s="8" t="n">
+        <v>717.5</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="Z11" s="3" t="inlineStr"/>
+        <v>80494</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1436,10 +1455,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>229</v>
+        <v>229.5</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>13.4</v>
@@ -1448,9 +1467,9 @@
         <v>17.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="H12" s="14" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H12" s="8" t="n">
         <v>13</v>
       </c>
       <c r="I12" s="3" t="n">
@@ -1462,50 +1481,46 @@
       <c r="K12" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="L12" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="M12" s="14" t="n">
-        <v>38.5</v>
+      <c r="L12" s="8" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="M12" s="15" t="n">
+        <v>83.90000000000001</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>12.8</v>
+        <v>931.8</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="11" t="n">
         <v>20.5</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="S12" s="3" t="n">
+      <c r="S12" s="8" t="n">
         <v>17.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="V12" s="13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W12" s="11" t="n">
-        <v>14.8</v>
-      </c>
+        <v>24.8</v>
+      </c>
+      <c r="U12" s="3" t="inlineStr"/>
+      <c r="V12" s="15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W12" s="13" t="inlineStr"/>
       <c r="X12" s="3" t="n">
-        <v>17.5</v>
+        <v>12.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>18.4</v>
+        <v>940.5</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1536,7 +1551,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>13.1</v>
+        <v>1.3</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.4</v>
@@ -1548,21 +1563,21 @@
         <v>15.7</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>16.9</v>
+        <v>16.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>94.5</v>
+        <v>92.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q13" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q13" s="11" t="n">
         <v>15.8</v>
       </c>
       <c r="R13" s="3" t="n">
@@ -1572,22 +1587,22 @@
         <v>16.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>20.5</v>
+        <v>20.9</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="W13" s="11" t="n">
-        <v>15.8</v>
+        <v>16.9</v>
+      </c>
+      <c r="W13" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>1.5</v>
+        <v>15.9</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.8</v>
@@ -1608,29 +1623,29 @@
       <c r="C14" s="3" t="n">
         <v>324</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E14" s="14" t="n">
+      <c r="D14" s="11" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E14" s="11" t="n">
         <v>13.4</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>11.4</v>
+      <c r="F14" s="11" t="n">
+        <v>17.6</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>86.8</v>
+        <v>56.8</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>14.4</v>
@@ -1639,40 +1654,40 @@
         <v>13.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>15.4</v>
+        <v>15.8</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>94</v>
+        <v>0.1</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" s="13" t="n">
-        <v>2.8</v>
+      <c r="Q14" s="11" t="n">
+        <v>21.7</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S14" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="U14" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="T14" s="3" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>7.2</v>
-      </c>
       <c r="V14" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="W14" s="11" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X14" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="W14" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X14" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>87.5</v>
+        <v>92</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>1.6</v>
@@ -1693,30 +1708,32 @@
       <c r="C15" s="3" t="n">
         <v>307.9</v>
       </c>
-      <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>7.5</v>
+      <c r="D15" s="11" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>18.9</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>12.6</v>
+        <v>13.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.2</v>
+        <v>12.4</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>13.8</v>
@@ -1725,12 +1742,12 @@
         <v>15.5</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>96.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Q15" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q15" s="11" t="n">
         <v>19.8</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1743,22 +1760,22 @@
         <v>73</v>
       </c>
       <c r="U15" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="X15" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="Y15" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W15" s="11" t="n">
+      <c r="Z15" s="3" t="n">
         <v>15.7</v>
-      </c>
-      <c r="X15" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Y15" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="Z15" s="3" t="n">
-        <v>1.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1774,76 +1791,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1973.2</v>
-      </c>
-      <c r="D16" s="9" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="D16" s="10" t="n">
         <v>114.8</v>
       </c>
-      <c r="E16" s="9" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>96</v>
+      <c r="E16" s="10" t="n">
+        <v>674.7</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>17.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>164.4</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="L16" s="9" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="L16" s="10" t="n">
         <v>73.2</v>
       </c>
-      <c r="M16" s="9" t="n">
-        <v>69.40000000000001</v>
+      <c r="M16" s="10" t="n">
+        <v>634.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>15.4</v>
+        <v>1140.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Q16" s="9" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="R16" s="9" t="n">
-        <v>61.4</v>
+      <c r="Q16" s="10" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="R16" s="10" t="n">
+        <v>83</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>88</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>3945.2</v>
+        <v>394.5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="V16" s="9" t="n">
-        <v>84</v>
-      </c>
-      <c r="W16" s="9" t="n">
-        <v>18.6</v>
+        <v>24.2</v>
+      </c>
+      <c r="V16" s="10" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="W16" s="10" t="n">
+        <v>78.59999999999999</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>85.09999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>428.8</v>
+        <v>1208.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>2.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1859,19 +1876,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1469.4</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>4.8</v>
+        <v>295</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.9</v>
+        <v>9.5</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.9</v>
@@ -1880,55 +1897,55 @@
         <v>1.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="L17" s="9" t="n">
+        <v>281.4</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="L17" s="10" t="n">
         <v>14.6</v>
       </c>
-      <c r="M17" s="9" t="n">
-        <v>13.9</v>
+      <c r="M17" s="10" t="n">
+        <v>19.1</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>15.8</v>
+        <v>18.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q17" s="9" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="R17" s="9" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="Q17" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="R17" s="10" t="n">
         <v>16.7</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="V17" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="V17" s="9" t="n">
+      <c r="W17" s="10" t="n">
         <v>16.9</v>
-      </c>
-      <c r="W17" s="11" t="n">
-        <v>15.7</v>
       </c>
       <c r="X17" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>21.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>2</v>
+        <v>15.3</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1944,51 +1961,49 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>428.8</v>
+        <v>428.3</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>24.9</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H18" s="3" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="H18" s="8" t="n">
         <v>10.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3" t="n">
+      <c r="K18" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L18" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="8" t="n">
         <v>13</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>19.4</v>
+        <v>14.4</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="P18" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q18" s="13" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="R18" s="3" t="n">
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R18" s="11" t="n">
         <v>17.8</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -1998,22 +2013,22 @@
         <v>69.09999999999999</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="V18" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="W18" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V18" s="11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W18" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="X18" s="14" t="n">
-        <v>17</v>
+      <c r="X18" s="8" t="n">
+        <v>70.09999999999999</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>81.8</v>
+        <v>84</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2031,49 +2046,49 @@
       <c r="C19" s="3" t="n">
         <v>440.6</v>
       </c>
-      <c r="D19" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="E19" s="3" t="n">
+      <c r="D19" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="11" t="n">
         <v>19.5</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>13</v>
+      <c r="G19" s="8" t="n">
+        <v>14</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K19" s="11" t="n">
+      <c r="K19" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="11" t="n">
         <v>15.1</v>
       </c>
-      <c r="M19" s="13" t="n">
+      <c r="M19" s="15" t="n">
         <v>1.4</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>46.4</v>
+        <v>15.5</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q19" s="13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R19" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="R19" s="11" t="n">
         <v>18.1</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2085,20 +2100,20 @@
       <c r="U19" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V19" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="W19" s="13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="X19" s="14" t="n">
-        <v>185.3</v>
+      <c r="V19" s="11" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="W19" s="15" t="n">
+        <v>87</v>
+      </c>
+      <c r="X19" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>81</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>127.4</v>
+        <v>17.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2117,49 +2132,49 @@
         <v>153.1</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>21.9</v>
+        <v>20.7</v>
       </c>
       <c r="E20" s="11" t="n">
         <v>13.8</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>17.9</v>
+        <v>17.3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>13</v>
+        <v>11.8</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K20" s="11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K20" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="L20" s="14" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>15.1</v>
+      <c r="L20" s="11" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="M20" s="15" t="n">
+        <v>45.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q20" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R20" s="13" t="n">
-        <v>87.59999999999999</v>
+        <v>9</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R20" s="11" t="n">
+        <v>17.6</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>18.5</v>
@@ -2168,13 +2183,13 @@
         <v>76.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="V20" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="V20" s="11" t="n">
         <v>17.6</v>
       </c>
-      <c r="W20" s="13" t="n">
-        <v>75.5</v>
+      <c r="W20" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>18.6</v>
@@ -2201,20 +2216,20 @@
       <c r="C21" s="3" t="n">
         <v>261.7</v>
       </c>
-      <c r="D21" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="E21" s="3" t="n">
+      <c r="D21" s="11" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E21" s="11" t="n">
         <v>14.7</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" s="11" t="n">
         <v>18.3</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>19.9</v>
+        <v>14.1</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>11.1</v>
@@ -2222,32 +2237,32 @@
       <c r="J21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K21" s="11" t="n">
+      <c r="K21" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="L21" s="13" t="n">
-        <v>56.2</v>
+      <c r="L21" s="11" t="n">
+        <v>16.2</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>121.3</v>
+        <v>11.7</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>90.8</v>
+        <v>99.8</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q21" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="R21" s="3" t="n">
+      <c r="Q21" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="R21" s="11" t="n">
         <v>18.1</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>43.1</v>
+        <v>18.9</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>74</v>
@@ -2255,17 +2270,17 @@
       <c r="U21" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V21" s="14" t="n">
-        <v>18.2</v>
+      <c r="V21" s="11" t="n">
+        <v>18.5</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>17</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>880.9</v>
+        <v>87</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>2.8</v>
@@ -2286,41 +2301,41 @@
       <c r="C22" s="3" t="n">
         <v>123.3</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="E22" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F22" s="3" t="n">
+      <c r="E22" s="11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F22" s="11" t="n">
         <v>17.5</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="H22" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H22" s="8" t="n">
         <v>13.4</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K22" s="11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K22" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="L22" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N22" s="14" t="n">
-        <v>68.90000000000001</v>
+      <c r="L22" s="11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="M22" s="15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>1</v>
+        <v>91.8</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>1.8</v>
@@ -2328,20 +2343,20 @@
       <c r="Q22" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="11" t="n">
         <v>17.2</v>
       </c>
-      <c r="S22" s="14" t="n">
+      <c r="S22" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>740.8</v>
+        <v>74</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="V22" s="3" t="n">
-        <v>12</v>
+      <c r="V22" s="11" t="n">
+        <v>17.5</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>16.9</v>
@@ -2350,10 +2365,10 @@
         <v>18.9</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>94.5</v>
+        <v>947</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1</v>
+        <v>10.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2369,51 +2384,49 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>477.4</v>
-      </c>
-      <c r="D23" s="9" t="n">
+        <v>177.2</v>
+      </c>
+      <c r="D23" s="11" t="n">
         <v>113.1</v>
       </c>
-      <c r="E23" s="9" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>91</v>
+      <c r="E23" s="10" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>91.8</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2654</v>
+        <v>94.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>636.4</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>80.8</v>
-      </c>
+        <v>61.2</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K23" s="11" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="L23" s="9" t="n">
-        <v>161.4</v>
-      </c>
-      <c r="M23" s="9" t="n">
-        <v>14.6</v>
+      <c r="K23" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>12.2</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>31.6</v>
+        <v>30.4</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q23" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q23" s="10" t="n">
         <v>109</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="11" t="n">
         <v>88.8</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2425,17 +2438,17 @@
       <c r="U23" s="3" t="n">
         <v>40.6</v>
       </c>
-      <c r="V23" s="9" t="n">
-        <v>919.8</v>
-      </c>
-      <c r="W23" s="9" t="n">
-        <v>83.90000000000001</v>
+      <c r="V23" s="11" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="W23" s="10" t="n">
+        <v>81.09999999999999</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>942.1</v>
+        <v>9</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>148.8</v>
+        <v>929.5</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>13.8</v>
@@ -2457,19 +2470,19 @@
         <v>215.4</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="E24" s="11" t="n">
         <v>13.9</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>636.4</v>
+        <v>12.9</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>1.5</v>
@@ -2478,28 +2491,28 @@
         <v>1.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="L24" s="9" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="M24" s="9" t="n">
-        <v>14.4</v>
+        <v>0.5</v>
+      </c>
+      <c r="L24" s="11" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="M24" s="10" t="n">
+        <v>43.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>221.1</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q24" s="10" t="n">
         <v>21.8</v>
       </c>
-      <c r="R24" s="9" t="n">
-        <v>47.8</v>
+      <c r="R24" s="11" t="n">
+        <v>17.8</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>18.1</v>
@@ -2510,14 +2523,14 @@
       <c r="U24" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V24" s="9" t="n">
+      <c r="V24" s="11" t="n">
         <v>18.3</v>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>87.09999999999999</v>
@@ -2539,76 +2552,74 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>130.4</v>
-      </c>
-      <c r="D25" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D25" s="11" t="n">
         <v>22.6</v>
       </c>
-      <c r="E25" s="13" t="n">
-        <v>64.31</v>
-      </c>
-      <c r="F25" s="3" t="n">
+      <c r="E25" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="F25" s="11" t="n">
         <v>18.8</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>12.9</v>
+        <v>1.1</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>2</v>
+        <v>10.1</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="L25" s="11" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="M25" s="14" t="n">
-        <v>34.2</v>
+      <c r="L25" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M25" s="15" t="n">
+        <v>84.2</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>910.8</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q25" s="11" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="R25" s="13" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="S25" s="14" t="n">
-        <v>17.6</v>
+        <v>91.5</v>
+      </c>
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>49.5</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="V25" s="11" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V25" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="W25" s="11" t="n">
         <v>15.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>18.1</v>
+        <v>1.4</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>94</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2624,16 +2635,16 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>87.8</v>
+        <v>32.6</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>23.4</v>
+        <v>22.5</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>14.3</v>
+        <v>13.6</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>18.9</v>
+        <v>18.1</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>8.9</v>
@@ -2642,19 +2653,19 @@
         <v>12.9</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="L26" s="11" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>14.9</v>
+        <v>3.9</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="M26" s="15" t="n">
+        <v>1.4</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>11.5</v>
@@ -2663,13 +2674,13 @@
         <v>95</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q26" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q26" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="R26" s="3" t="n">
-        <v>17.3</v>
+      <c r="R26" s="8" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>17.8</v>
@@ -2680,20 +2691,20 @@
       <c r="U26" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V26" s="11" t="n">
+      <c r="V26" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="W26" s="11" t="n">
         <v>16.5</v>
       </c>
-      <c r="X26" s="3" t="n">
+      <c r="X26" s="8" t="n">
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>2.5</v>
+        <v>88.5</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>1.6</v>
+        <v>12.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2709,49 +2720,47 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>14.1</v>
+        <v>12.8</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>18.9</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>9.1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>1.4</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="L27" s="11" t="n">
+      <c r="L27" s="8" t="n">
         <v>15.4</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.6</v>
+        <v>18.8</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>94</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q27" s="11" t="n">
-        <v>20.8</v>
+        <v>1.2</v>
+      </c>
+      <c r="Q27" s="8" t="n">
+        <v>10.8</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>17.9</v>
@@ -2760,16 +2769,16 @@
         <v>19</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>71</v>
+        <v>717</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="V27" s="11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V27" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="W27" s="11" t="n">
-        <v>15.8</v>
+        <v>16.8</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>18.5</v>
@@ -2794,40 +2803,40 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>305.9</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E28" s="3" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E28" s="11" t="n">
         <v>13.8</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>11.9</v>
+      <c r="F28" s="11" t="n">
+        <v>17.8</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="L28" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K28" s="8" t="n">
         <v>15.4</v>
       </c>
-      <c r="M28" s="3" t="n">
+      <c r="L28" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M28" s="8" t="n">
         <v>14.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.4</v>
+        <v>18.5</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>95</v>
@@ -2835,14 +2844,14 @@
       <c r="P28" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q28" s="11" t="n">
-        <v>20.5</v>
+      <c r="Q28" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>17</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>17.2</v>
+        <v>41.5</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>72.8</v>
@@ -2850,7 +2859,7 @@
       <c r="U28" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V28" s="11" t="n">
+      <c r="V28" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="W28" s="11" t="n">
@@ -2863,7 +2872,7 @@
         <v>83.8</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>3.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2882,45 +2891,45 @@
         <v>289.8</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>21.9</v>
+        <v>21.2</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>13.8</v>
+        <v>13.1</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>17.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>84.5</v>
+        <v>8.1</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>23.8</v>
+        <v>13.8</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="L29" s="11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="L29" s="8" t="n">
         <v>14.9</v>
       </c>
-      <c r="M29" s="13" t="n">
-        <v>84.40000000000001</v>
+      <c r="M29" s="3" t="n">
+        <v>14.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.6</v>
+        <v>11.1</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>95</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q29" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q29" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="R29" s="3" t="n">
@@ -2930,19 +2939,19 @@
         <v>18.2</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>10</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="V29" s="11" t="n">
+      <c r="V29" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="W29" s="11" t="n">
         <v>17.1</v>
       </c>
-      <c r="X29" s="3" t="n">
-        <v>18.2</v>
+      <c r="X29" s="8" t="n">
+        <v>82.09999999999999</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>85</v>
@@ -2964,73 +2973,69 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1689.9</v>
-      </c>
-      <c r="D30" s="9" t="n">
+        <v>1609.9</v>
+      </c>
+      <c r="D30" s="10" t="n">
         <v>1129.8</v>
       </c>
-      <c r="E30" s="9" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="F30" s="9" t="n">
+      <c r="E30" s="14" t="inlineStr"/>
+      <c r="F30" s="10" t="n">
         <v>90.59999999999999</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>43.7</v>
+        <v>49.7</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="K30" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="K30" s="10" t="n">
         <v>38.6</v>
       </c>
-      <c r="L30" s="9" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="M30" s="9" t="n">
+      <c r="L30" s="14" t="inlineStr"/>
+      <c r="M30" s="10" t="n">
         <v>11.7</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>1.6</v>
+        <v>7.9</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>479.8</v>
+        <v>0.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q30" s="9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Q30" s="10" t="n">
         <v>105.2</v>
       </c>
-      <c r="R30" s="9" t="n">
-        <v>27.4</v>
+      <c r="R30" s="10" t="n">
+        <v>87.40000000000001</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>90.09999999999999</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>561.8</v>
+        <v>561</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>394.6</v>
-      </c>
-      <c r="V30" s="9" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="W30" s="9" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="V30" s="10" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="W30" s="11" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>88</v>
+        <v>88.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>416.8</v>
+        <v>441</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>12.2</v>
@@ -3064,7 +3069,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>28.2</v>
+        <v>18.3</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>1.3</v>
@@ -3072,53 +3077,49 @@
       <c r="J31" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="L31" s="11" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="M31" s="9" t="n">
-        <v>1.4</v>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="10" t="n">
+        <v>14.7</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>16.1</v>
+        <v>0.5</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>16.8</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" s="11" t="n">
+      <c r="Q31" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="R31" s="9" t="n">
+      <c r="R31" s="10" t="n">
         <v>17.5</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>116.3</v>
+        <v>29.3</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="V31" s="11" t="n">
-        <v>17.6</v>
+        <v>6.9</v>
+      </c>
+      <c r="V31" s="10" t="n">
+        <v>18.6</v>
       </c>
       <c r="W31" s="11" t="n">
         <v>16.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>17.7</v>
+        <v>1.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>88.3</v>
+        <v>119.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>4.4</v>
+        <v>214.4</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3134,40 +3135,38 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>481.8</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>24.9</v>
-      </c>
+        <v>23.5</v>
+      </c>
+      <c r="D32" s="13" t="inlineStr"/>
       <c r="E32" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>71.90000000000001</v>
+        <v>14.2</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>19.4</v>
+        <v>13.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="M32" s="13" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M32" s="15" t="n">
         <v>10.51</v>
       </c>
-      <c r="N32" s="3" t="n">
-        <v>16.1</v>
+      <c r="N32" s="8" t="n">
+        <v>12.8</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>83</v>
@@ -3178,14 +3177,14 @@
       <c r="Q32" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="R32" s="14" t="n">
-        <v>15.8</v>
+      <c r="R32" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>18.8</v>
+        <v>18.2</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>2.2</v>
@@ -3197,13 +3196,13 @@
         <v>15.6</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>17.7</v>
+        <v>18.8</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3219,46 +3218,46 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>422.8</v>
-      </c>
-      <c r="D33" s="13" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="E33" s="13" t="n">
-        <v>6618.45</v>
+        <v>1482.8</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="G33" s="14" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>20.6</v>
+        <v>19.5</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>82.59999999999999</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>4.9</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>12.9</v>
+        <v>86.5</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>16.1</v>
+        <v>13.7</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="N33" s="14" t="n">
-        <v>92.40000000000001</v>
+      <c r="N33" s="8" t="n">
+        <v>84.8</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>93</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>23.8</v>
@@ -3270,7 +3269,7 @@
         <v>12.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>319.5</v>
+        <v>21.2</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>14.4</v>
@@ -3278,11 +3277,11 @@
       <c r="V33" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="W33" s="14" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>16.6</v>
+      <c r="W33" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="X33" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="Y33" s="3" t="n">
         <v>71</v>
@@ -3304,28 +3303,28 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>492.8</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="E34" s="13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="G34" s="3" t="n">
+        <v>482.8</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="G34" s="8" t="n">
         <v>12.6</v>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>18.3</v>
+      <c r="H34" s="8" t="n">
+        <v>109.5</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0</v>
@@ -3333,11 +3332,11 @@
       <c r="L34" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M34" s="13" t="n">
-        <v>91.59999999999999</v>
+      <c r="M34" s="8" t="n">
+        <v>11.6</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>92</v>
@@ -3348,8 +3347,8 @@
       <c r="Q34" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="R34" s="13" t="n">
-        <v>1.7</v>
+      <c r="R34" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>16.8</v>
@@ -3364,15 +3363,15 @@
         <v>18</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X34" s="3" t="inlineStr"/>
+        <v>12.8</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y34" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="Z34" s="3" t="n">
-        <v>4.2</v>
-      </c>
+      <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -3387,25 +3386,25 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="D35" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="E35" s="14" t="n">
+        <v>9492.799999999999</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E35" s="11" t="n">
         <v>13.6</v>
       </c>
-      <c r="F35" s="13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G35" s="14" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>0.4</v>
+      <c r="F35" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>279.3</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>2.4</v>
+        <v>44.6</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>4</v>
@@ -3417,19 +3416,19 @@
         <v>16.6</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>17.8</v>
+        <v>11.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>90</v>
+        <v>910</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q35" s="3" t="n">
-        <v>24.8</v>
+      <c r="Q35" s="15" t="n">
+        <v>94.5</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>18.8</v>
@@ -3438,22 +3437,22 @@
         <v>18.2</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>60</v>
+        <v>600.8</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="V35" s="11" t="n">
         <v>20.7</v>
       </c>
-      <c r="W35" s="13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X35" s="3" t="n">
-        <v>18.5</v>
+      <c r="W35" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>82.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>75.5</v>
+        <v>125.5</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>6</v>
@@ -3472,25 +3471,25 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>498.3</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E36" s="3" t="n">
+        <v>9498.9</v>
+      </c>
+      <c r="D36" s="15" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="E36" s="8" t="n">
         <v>13.9</v>
       </c>
-      <c r="F36" s="13" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>10.3</v>
+      <c r="F36" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>410.3</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.4</v>
+        <v>12.7</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>4</v>
@@ -3498,14 +3497,14 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="3" t="n">
-        <v>16.6</v>
+      <c r="L36" s="15" t="n">
+        <v>86.59999999999999</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="N36" s="14" t="n">
-        <v>81.09999999999999</v>
+      <c r="N36" s="8" t="n">
+        <v>17.4</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>91</v>
@@ -3513,20 +3512,20 @@
       <c r="P36" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q36" s="3" t="n">
-        <v>29.2</v>
+      <c r="Q36" s="15" t="n">
+        <v>88.09999999999999</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>55.1</v>
+        <v>52.1</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>12.8</v>
+        <v>11.2</v>
       </c>
       <c r="V36" s="11" t="n">
         <v>18.4</v>
@@ -3534,14 +3533,14 @@
       <c r="W36" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="X36" s="3" t="n">
-        <v>1.6</v>
+      <c r="X36" s="8" t="n">
+        <v>66.59999999999999</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3557,76 +3556,74 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>128.1</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>92.59999999999999</v>
+        <v>2192.8</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>665.7</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>9.4</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>18.8</v>
-      </c>
+        <v>53.3</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="3" t="n">
         <v>110.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <v>121.8</v>
-      </c>
-      <c r="L37" s="9" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="M37" s="9" t="n">
-        <v>15.6</v>
+        <v>17.6</v>
+      </c>
+      <c r="K37" s="10" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="L37" s="10" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="M37" s="10" t="n">
+        <v>711.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>11.1</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>44930.3</v>
+        <v>4420.3</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q37" s="9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q37" s="10" t="n">
         <v>113.4</v>
       </c>
-      <c r="R37" s="9" t="n">
+      <c r="R37" s="10" t="n">
         <v>81</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>24.8</v>
+        <v>84.8</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>313.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>24.8</v>
+        <v>234.8</v>
       </c>
       <c r="V37" s="11" t="n">
         <v>91</v>
       </c>
-      <c r="W37" s="9" t="n">
-        <v>80.90000000000001</v>
+      <c r="W37" s="10" t="n">
+        <v>80.40000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>83.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>41252.4</v>
+        <v>409.8</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>4.5</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3642,58 +3639,56 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>438.6</v>
+        <v>43.8</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>23.8</v>
+        <v>23.1</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>18</v>
+        <v>18.9</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>18.5</v>
+        <v>10.8</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>22.3</v>
+        <v>12.3</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2.1</v>
+        <v>12.1</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K38" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L38" s="9" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="M38" s="9" t="n">
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="10" t="n">
+        <v>151.3</v>
+      </c>
+      <c r="M38" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="N38" s="14" t="n">
-        <v>58.1</v>
+      <c r="N38" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>89.8</v>
+        <v>15.2</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q38" s="9" t="n">
+      <c r="Q38" s="10" t="n">
         <v>22.7</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" s="10" t="n">
         <v>17.4</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>480.5</v>
+        <v>17</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>63.9</v>
+        <v>82.7</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>11</v>
@@ -3701,17 +3696,17 @@
       <c r="V38" s="11" t="n">
         <v>18.2</v>
       </c>
-      <c r="W38" s="9" t="n">
-        <v>15.1</v>
+      <c r="W38" s="10" t="n">
+        <v>16.1</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>21.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>4</v>
+        <v>89.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3727,76 +3722,72 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>2392.3</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E39" s="14" t="n">
-        <v>23</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G39" s="14" t="n">
-        <v>11.9</v>
+        <v>39595.3</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>11.5</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>5.2</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="L39" s="13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N39" s="14" t="n">
-        <v>1.5</v>
+        <v>0</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>29.6</v>
+        <v>23.6</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="S39" s="3" t="n">
-        <v>19</v>
+      <c r="S39" s="8" t="n">
+        <v>20.9</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>52</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="V39" s="13" t="n">
-        <v>1.9</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="V39" s="13" t="inlineStr"/>
       <c r="W39" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="X39" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="X39" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>71</v>
+        <v>1.4</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>6.9</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3812,42 +3803,46 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2942.1</v>
-      </c>
-      <c r="D40" s="13" t="n">
-        <v>49.2</v>
+        <v>545.4</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>29.3</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F40" s="13" t="n">
-        <v>4.9</v>
+        <v>12.8</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="12" t="inlineStr"/>
+        <v>0.3</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="L40" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M40" s="14" t="n">
-        <v>12</v>
+      <c r="M40" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>23.8</v>
@@ -3856,7 +3851,7 @@
         <v>17.9</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>58.8</v>
@@ -3867,17 +3862,17 @@
       <c r="V40" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="W40" s="3" t="n">
-        <v>12.1</v>
+      <c r="W40" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>16.8</v>
+        <v>1.6</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>6.2</v>
+        <v>408.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3893,28 +3888,28 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>408.4</v>
+        <v>340.1</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>13.7</v>
+        <v>23.7</v>
       </c>
       <c r="E41" s="11" t="n">
         <v>12.5</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>13.1</v>
+        <v>18.1</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H41" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H41" s="8" t="n">
         <v>10.8</v>
       </c>
-      <c r="I41" s="14" t="n">
-        <v>81</v>
+      <c r="I41" s="3" t="n">
+        <v>2.4</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
@@ -3922,45 +3917,47 @@
       <c r="L41" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="M41" s="13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N41" s="3" t="inlineStr"/>
+      <c r="M41" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="O41" s="3" t="n">
-        <v>82</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" s="13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R41" s="13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>17.8</v>
+      <c r="Q41" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="S41" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.5</v>
+        <v>62.2</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>1</v>
+        <v>10.6</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>19</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>18.2</v>
+        <v>14.6</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>83</v>
+        <v>113.8</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>19.2</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3976,50 +3973,52 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>340.1</v>
+        <v>331</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>22.4</v>
+        <v>22.9</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>14.7</v>
+        <v>14.1</v>
       </c>
       <c r="F42" s="11" t="n">
         <v>18.5</v>
       </c>
-      <c r="G42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="H42" s="3" t="n">
-        <v>13.7</v>
+        <v>11.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="M42" s="13" t="n">
-        <v>1.3</v>
+        <v>16.2</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>15.1</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>14.6</v>
+        <v>16.1</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="R42" s="13" t="n">
-        <v>4.8</v>
+        <v>22</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>16.7</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>16</v>
@@ -4031,17 +4030,19 @@
         <v>10.4</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>18.2</v>
+        <v>20.4</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X42" s="3" t="inlineStr"/>
+        <v>12.1</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="Y42" s="3" t="n">
-        <v>87</v>
+        <v>110.1</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>2.6</v>
+        <v>58</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4057,74 +4058,76 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>537</v>
-      </c>
-      <c r="D43" s="13" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="E43" s="12" t="inlineStr"/>
+        <v>557.1</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>1.2</v>
+      </c>
       <c r="F43" s="3" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>11.7</v>
+        <v>10.8</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>99.59999999999999</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>1.4</v>
+        <v>28.8</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>15.1</v>
+        <v>14.2</v>
+      </c>
+      <c r="M43" s="8" t="n">
+        <v>35.4</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R43" s="13" t="n">
-        <v>1.6</v>
+      <c r="R43" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>15.6</v>
+        <v>12.6</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W43" s="13" t="n">
-        <v>0.1</v>
+        <v>186.7</v>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="V43" s="15" t="n">
+        <v>91</v>
+      </c>
+      <c r="W43" s="8" t="n">
+        <v>22.6</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>16.2</v>
+        <v>5</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>81.8</v>
+        <v>1.9</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4140,63 +4143,77 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>223.1</v>
-      </c>
-      <c r="D44" s="11" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E44" s="11" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F44" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="G44" s="3" t="inlineStr"/>
+        <v>2983</v>
+      </c>
+      <c r="D44" s="15" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>62</v>
+      </c>
       <c r="H44" s="3" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>2.6</v>
+        <v>15.2</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>5</v>
+        <v>26.2</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>15.1</v>
+        <v>1.1</v>
+      </c>
+      <c r="L44" s="15" t="n">
+        <v>83.59999999999999</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="n">
+        <v>19.1</v>
+      </c>
       <c r="O44" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="P44" s="3" t="n">
-        <v>1.4</v>
+        <v>8.1</v>
+      </c>
+      <c r="P44" s="8" t="n">
+        <v>340.9</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="R44" s="13" t="n">
-        <v>67.09999999999999</v>
+        <v>10.6</v>
+      </c>
+      <c r="R44" s="15" t="n">
+        <v>2.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>13.9</v>
+        <v>97.5</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="14" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="W44" s="12" t="inlineStr"/>
-      <c r="X44" s="3" t="inlineStr"/>
-      <c r="Y44" s="3" t="inlineStr"/>
-      <c r="Z44" s="3" t="inlineStr"/>
+        <v>351</v>
+      </c>
+      <c r="U44" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="V44" s="15" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="W44" s="15" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="Y44" s="3" t="n">
+        <v>466.8</v>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v>28.1</v>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4211,76 +4228,76 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2282</v>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>1981.8</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>110.8</v>
+        <v>497</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>18.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>62</v>
+        <v>10.3</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>20.8</v>
+        <v>11.8</v>
       </c>
       <c r="I45" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="K45" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L45" s="10" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="M45" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N45" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="J45" s="3" t="n">
-        <v>286.2</v>
-      </c>
-      <c r="K45" s="9" t="n">
-        <v>180.1</v>
-      </c>
-      <c r="L45" s="9" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="M45" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>31.3</v>
-      </c>
       <c r="O45" s="3" t="n">
-        <v>240.9</v>
+        <v>10.1</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q45" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="R45" s="9" t="n">
-        <v>10.4</v>
+        <v>0.8</v>
+      </c>
+      <c r="Q45" s="10" t="n">
+        <v>922.8</v>
+      </c>
+      <c r="R45" s="10" t="n">
+        <v>17.1</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>92.2</v>
+        <v>16.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>331</v>
+        <v>58.5</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>162</v>
-      </c>
-      <c r="V45" s="9" t="n">
-        <v>119.8</v>
-      </c>
-      <c r="W45" s="9" t="n">
-        <v>22</v>
+        <v>11.5</v>
+      </c>
+      <c r="V45" s="10" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="W45" s="10" t="n">
+        <v>15.9</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>36</v>
+        <v>16.6</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>966.8</v>
+        <v>82.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>28.7</v>
+        <v>44.8</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4298,70 +4315,74 @@
       <c r="C46" s="3" t="n">
         <v>497</v>
       </c>
-      <c r="D46" s="11" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E46" s="11" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="F46" s="11" t="n">
-        <v>18</v>
+      <c r="D46" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F46" s="15" t="n">
+        <v>0.1</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10.3</v>
+        <v>145.9</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>11.8</v>
+        <v>1.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="9" t="n">
+      <c r="K46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L46" s="10" t="n">
         <v>14.9</v>
       </c>
-      <c r="M46" s="9" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>6.8</v>
+      <c r="M46" s="10" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N46" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>20.4</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q46" s="9" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="R46" s="9" t="n">
-        <v>17.1</v>
+      <c r="Q46" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R46" s="10" t="n">
+        <v>1.8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>16.2</v>
+        <v>1</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="U46" s="3" t="inlineStr"/>
-      <c r="V46" s="9" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="W46" s="9" t="n">
-        <v>15.9</v>
+        <v>11.8</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>1414</v>
+      </c>
+      <c r="V46" s="10" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="W46" s="10" t="n">
+        <v>11151.1</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>16.6</v>
+        <v>0.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>77.8</v>
+        <v>112</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>4.8</v>
+        <v>15.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_correct_values.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_correct_values.xlsx
@@ -53,14 +53,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -155,13 +155,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -173,7 +170,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -789,13 +786,13 @@
       <c r="C4" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="12" t="n">
         <v>13.5</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="12" t="n">
         <v>19.4</v>
       </c>
       <c r="G4" s="3" t="n">
@@ -816,11 +813,11 @@
       <c r="L4" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="M4" s="11" t="n">
+      <c r="M4" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>29.5</v>
+      <c r="N4" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>87</v>
@@ -828,7 +825,7 @@
       <c r="P4" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q4" s="11" t="n">
+      <c r="Q4" s="3" t="n">
         <v>25</v>
       </c>
       <c r="R4" s="3" t="n">
@@ -838,13 +835,13 @@
         <v>16.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v>18.7</v>
+        <v>1.5</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="W4" s="11" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
@@ -864,76 +861,76 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="F5" s="11" t="n">
+        <v>388.3</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F5" s="12" t="n">
         <v>19.1</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="H5" s="8" t="n">
-        <v>12.8</v>
+      <c r="H5" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="L5" s="15" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="M5" s="11" t="n">
+      <c r="L5" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M5" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>12.1</v>
+        <v>18.1</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="Q5" s="11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q5" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.6</v>
+        <v>13.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>52</v>
+        <v>61.5</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="W5" s="11" t="n">
-        <v>17.6</v>
+        <v>13</v>
+      </c>
+      <c r="W5" s="9" t="n">
+        <v>2.4</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>18.4</v>
+        <v>13.9</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>75.5</v>
+        <v>12.8</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -949,48 +946,48 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>18.5</v>
+        <v>508.9</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>13.2</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>13.9</v>
+        <v>12</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="M6" s="11" t="n">
-        <v>13.1</v>
+        <v>14.3</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>13.6</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>45.1</v>
+        <v>15.9</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>1.1</v>
+        <v>22.5</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q6" s="11" t="n">
+      <c r="Q6" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="R6" s="3" t="n">
@@ -1000,25 +997,25 @@
         <v>1.7</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>61.5</v>
+        <v>18.5</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>10.4</v>
+        <v>512.9</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="W6" s="11" t="n">
-        <v>16.8</v>
+        <v>10.7</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>18.1</v>
+        <v>17.6</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>27</v>
+        <v>17.4</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1034,76 +1031,76 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>512.9</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>18.5</v>
+        <v>22.9</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>17.6</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>10.7</v>
+        <v>7.7</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>8.4</v>
+        <v>1.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>98</v>
+        <v>29.9</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="M7" s="11" t="n">
-        <v>13.6</v>
+        <v>15.1</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>15.8</v>
+        <v>40.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>52.4</v>
+        <v>22.4</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="11" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="R7" s="15" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>17.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>12.4</v>
+        <v>18.3</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>59.1</v>
+        <v>64</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="V7" s="15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W7" s="11" t="n">
-        <v>16.6</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>17.7</v>
+        <v>76</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>82.5</v>
+        <v>28</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1119,76 +1116,76 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>229.8</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>17.6</v>
+        <v>22.2</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>7.7</v>
+        <v>50.9</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.9</v>
+        <v>63.1</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.9</v>
+        <v>706.4</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.8</v>
+        <v>260.4</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="M8" s="11" t="n">
-        <v>14.1</v>
+        <v>51.1</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>60.2</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>40.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>11.6</v>
+        <v>59</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q8" s="11" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="R8" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Q8" s="9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="R8" s="9" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="S8" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="W8" s="11" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="Y8" s="3" t="n">
-        <v>11.4</v>
+        <v>90</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1204,75 +1201,77 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>222.4</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>1118.5</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>93.09999999999999</v>
+        <v>445</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>18.6</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>30.9</v>
+        <v>10.2</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>63.1</v>
+        <v>12.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>706.4</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>260.4</v>
-      </c>
-      <c r="K9" s="10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K9" s="14" t="n">
         <v>51.1</v>
       </c>
-      <c r="L9" s="10" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="M9" s="10" t="n">
-        <v>0.2</v>
+      <c r="L9" s="14" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M9" s="14" t="n">
+        <v>13.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>166.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>59</v>
+        <v>21.8</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Q9" s="11" t="n">
-        <v>114</v>
-      </c>
-      <c r="R9" s="10" t="n">
-        <v>88.09999999999999</v>
+        <v>1.3</v>
+      </c>
+      <c r="Q9" s="14" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="R9" s="14" t="n">
+        <v>17.6</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>86.2</v>
+        <v>17.2</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>212.6</v>
+        <v>21.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="V9" s="10" t="n">
-        <v>115.1</v>
-      </c>
-      <c r="W9" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V9" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="W9" s="14" t="n">
         <v>16</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>117.8</v>
+        <v>89.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="Z9" s="3" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1287,74 +1286,76 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="D10" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>23.7</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="12" t="n">
         <v>13.5</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="12" t="n">
         <v>18.6</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>12.6</v>
+        <v>1.2</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>97.90000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="J10" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="K10" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="10" t="n">
+      <c r="L10" s="14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M10" s="14" t="n">
         <v>14.7</v>
       </c>
-      <c r="M10" s="11" t="n">
+      <c r="N10" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="N10" s="3" t="n">
-        <v>15.8</v>
-      </c>
       <c r="O10" s="3" t="n">
-        <v>99.8</v>
+        <v>15.3</v>
       </c>
       <c r="P10" s="3" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="Q10" s="14" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q10" s="11" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="R10" s="10" t="n">
+      <c r="R10" s="14" t="n">
         <v>17.6</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>19.6</v>
+        <v>21.5</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V10" s="10" t="n">
+      <c r="V10" s="14" t="n">
         <v>18.8</v>
       </c>
-      <c r="W10" s="11" t="n">
+      <c r="W10" s="14" t="n">
         <v>16.8</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>83</v>
+        <v>3.8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1372,17 +1373,17 @@
       <c r="C11" s="3" t="n">
         <v>191.8</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="12" t="n">
         <v>22.5</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="12" t="n">
         <v>13.7</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="12" t="n">
         <v>18.1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>28.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>14.8</v>
@@ -1394,53 +1395,43 @@
         <v>0.7</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="M11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M11" s="12" t="n">
         <v>14</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>11.9</v>
+        <v>17.2</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q11" s="11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="R11" s="15" t="n">
-        <v>1.1</v>
+      <c r="Q11" s="12" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="R11" s="12" t="n">
+        <v>17.5</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>140649.1</v>
+        <v>212.4</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>55.1</v>
       </c>
-      <c r="V11" s="3" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="W11" s="15" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="X11" s="8" t="n">
-        <v>717.5</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>80494</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>3.8</v>
-      </c>
+      <c r="V11" s="11" t="inlineStr"/>
+      <c r="W11" s="11" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1457,19 +1448,19 @@
       <c r="C12" s="3" t="n">
         <v>229.5</v>
       </c>
-      <c r="D12" s="11" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="E12" s="11" t="n">
+      <c r="D12" s="12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E12" s="12" t="n">
         <v>13.4</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="3" t="n">
         <v>13</v>
       </c>
       <c r="I12" s="3" t="n">
@@ -1481,40 +1472,40 @@
       <c r="K12" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="L12" s="8" t="n">
+      <c r="L12" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="M12" s="15" t="n">
-        <v>83.90000000000001</v>
+      <c r="M12" s="12" t="n">
+        <v>13.5</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>15</v>
+        <v>15.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>931.8</v>
+        <v>98</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q12" s="11" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="R12" s="3" t="n">
+      <c r="Q12" s="12" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R12" s="12" t="n">
         <v>17.1</v>
       </c>
-      <c r="S12" s="8" t="n">
+      <c r="S12" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>24.8</v>
+        <v>74.5</v>
       </c>
       <c r="U12" s="3" t="inlineStr"/>
-      <c r="V12" s="15" t="n">
+      <c r="V12" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="W12" s="13" t="inlineStr"/>
+      <c r="W12" s="11" t="inlineStr"/>
       <c r="X12" s="3" t="n">
-        <v>12.3</v>
+        <v>18.5</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>940.5</v>
@@ -1538,20 +1529,20 @@
       <c r="C13" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="12" t="n">
         <v>23.6</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="12" t="n">
         <v>13.8</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="12" t="n">
         <v>18.7</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>1.3</v>
+        <v>13.5</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.4</v>
@@ -1565,35 +1556,35 @@
       <c r="L13" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="12" t="n">
         <v>14.4</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>92.5</v>
+        <v>94.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q13" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="12" t="n">
         <v>15.8</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="12" t="n">
         <v>14.8</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>20.9</v>
+        <v>74.5</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>16.9</v>
+        <v>16.5</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>14.8</v>
@@ -1621,15 +1612,15 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>324</v>
-      </c>
-      <c r="D14" s="11" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="D14" s="12" t="n">
         <v>21.8</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="12" t="n">
         <v>13.4</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="12" t="n">
         <v>17.6</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -1639,58 +1630,58 @@
         <v>12.5</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>56.8</v>
+        <v>26.8</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="12" t="n">
         <v>13.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.1</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" s="11" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R14" s="3" t="n">
+      <c r="Q14" s="12" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="R14" s="12" t="n">
         <v>17.6</v>
       </c>
       <c r="S14" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="W14" s="8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="W14" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="X14" s="8" t="n">
+      <c r="X14" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>92</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>1.6</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1708,49 +1699,49 @@
       <c r="C15" s="3" t="n">
         <v>307.9</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="12" t="n">
         <v>24.6</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="F15" s="11" t="n">
+      <c r="E15" s="12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F15" s="12" t="n">
         <v>18.9</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>13.6</v>
+        <v>12.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>12.4</v>
+        <v>1.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="M15" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M15" s="12" t="n">
         <v>13.8</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>25</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q15" s="11" t="n">
+      <c r="Q15" s="12" t="n">
         <v>19.8</v>
       </c>
-      <c r="R15" s="3" t="n">
+      <c r="R15" s="12" t="n">
         <v>16.5</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1760,7 +1751,7 @@
         <v>73</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>18.2</v>
@@ -1793,50 +1784,50 @@
       <c r="C16" s="3" t="n">
         <v>147.5</v>
       </c>
-      <c r="D16" s="10" t="n">
-        <v>114.8</v>
-      </c>
-      <c r="E16" s="10" t="n">
+      <c r="D16" s="14" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E16" s="14" t="n">
         <v>674.7</v>
       </c>
-      <c r="F16" s="10" t="n">
-        <v>9.199999999999999</v>
+      <c r="F16" s="14" t="n">
+        <v>92.2</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>47.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>164.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>5.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="K16" s="10" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="L16" s="10" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K16" s="14" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="L16" s="14" t="n">
         <v>73.2</v>
       </c>
-      <c r="M16" s="10" t="n">
+      <c r="M16" s="14" t="n">
         <v>634.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1140.4</v>
+        <v>12.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Q16" s="10" t="n">
+      <c r="Q16" s="12" t="n">
         <v>96.5</v>
       </c>
-      <c r="R16" s="10" t="n">
-        <v>83</v>
+      <c r="R16" s="12" t="n">
+        <v>83.5</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>88.09999999999999</v>
@@ -1845,19 +1836,19 @@
         <v>394.5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="V16" s="10" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="V16" s="14" t="n">
         <v>84.3</v>
       </c>
-      <c r="W16" s="10" t="n">
+      <c r="W16" s="14" t="n">
         <v>78.59999999999999</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1208.8</v>
+        <v>158.8</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1876,16 +1867,16 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>295</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>29.5</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>12.1</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>9.5</v>
@@ -1897,30 +1888,30 @@
         <v>1.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>281.4</v>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="L17" s="10" t="n">
+        <v>121.4</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="L17" s="14" t="n">
         <v>14.6</v>
       </c>
-      <c r="M17" s="10" t="n">
-        <v>19.1</v>
+      <c r="M17" s="12" t="n">
+        <v>13.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>18.1</v>
+        <v>15.2</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q17" s="11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q17" s="12" t="n">
         <v>19.3</v>
       </c>
-      <c r="R17" s="10" t="n">
+      <c r="R17" s="12" t="n">
         <v>16.7</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1930,19 +1921,19 @@
         <v>92.90000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="V17" s="10" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="V17" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="W17" s="10" t="n">
+      <c r="W17" s="14" t="n">
         <v>16.9</v>
       </c>
       <c r="X17" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>21.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>15.3</v>
@@ -1961,25 +1952,25 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>428.3</v>
-      </c>
-      <c r="D18" s="11" t="n">
+        <v>428.5</v>
+      </c>
+      <c r="D18" s="12" t="n">
         <v>24.9</v>
       </c>
-      <c r="E18" s="11" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F18" s="11" t="n">
+      <c r="E18" s="12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F18" s="12" t="n">
         <v>18.7</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>48.4</v>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="H18" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.6</v>
@@ -1987,10 +1978,10 @@
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="11" t="n">
+      <c r="L18" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="M18" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -2000,10 +1991,10 @@
         <v>91</v>
       </c>
       <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="15" t="n">
+      <c r="Q18" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="R18" s="11" t="n">
+      <c r="R18" s="12" t="n">
         <v>17.8</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -2013,16 +2004,16 @@
         <v>69.09999999999999</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="V18" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="V18" s="12" t="n">
         <v>18.5</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="X18" s="8" t="n">
-        <v>70.09999999999999</v>
+      <c r="X18" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>84</v>
@@ -2044,18 +2035,18 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>440.6</v>
-      </c>
-      <c r="D19" s="11" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="D19" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="12" t="n">
         <v>19.5</v>
       </c>
-      <c r="G19" s="8" t="n">
+      <c r="G19" s="3" t="n">
         <v>14</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2070,25 +2061,25 @@
       <c r="K19" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="L19" s="11" t="n">
+      <c r="L19" s="12" t="n">
         <v>15.1</v>
       </c>
-      <c r="M19" s="15" t="n">
-        <v>1.4</v>
+      <c r="M19" s="3" t="n">
+        <v>14.3</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q19" s="8" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="R19" s="11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="R19" s="12" t="n">
         <v>18.1</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2100,11 +2091,11 @@
       <c r="U19" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V19" s="11" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="W19" s="15" t="n">
-        <v>87</v>
+      <c r="V19" s="12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W19" s="12" t="n">
+        <v>17.2</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>18.3</v>
@@ -2113,7 +2104,7 @@
         <v>81</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>17.4</v>
+        <v>4.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2131,49 +2122,49 @@
       <c r="C20" s="3" t="n">
         <v>153.1</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="12" t="n">
         <v>20.7</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="12" t="n">
         <v>13.8</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="12" t="n">
         <v>17.3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>11.8</v>
+        <v>8.9</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>23.8</v>
+        <v>13.8</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="L20" s="11" t="n">
+      <c r="L20" s="12" t="n">
         <v>15.4</v>
       </c>
-      <c r="M20" s="15" t="n">
+      <c r="M20" s="9" t="n">
         <v>45.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.4</v>
+        <v>17.8</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>9</v>
+        <v>0.5</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="R20" s="11" t="n">
+      <c r="R20" s="12" t="n">
         <v>17.6</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2185,10 +2176,10 @@
       <c r="U20" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="V20" s="11" t="n">
+      <c r="V20" s="12" t="n">
         <v>17.6</v>
       </c>
-      <c r="W20" s="3" t="n">
+      <c r="W20" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2214,51 +2205,51 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>261.7</v>
-      </c>
-      <c r="D21" s="11" t="n">
+        <v>251.7</v>
+      </c>
+      <c r="D21" s="12" t="n">
         <v>21.9</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="12" t="n">
         <v>14.7</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="12" t="n">
         <v>18.3</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="L21" s="11" t="n">
+      <c r="L21" s="12" t="n">
         <v>16.2</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>11.7</v>
+        <v>1.6</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>99.8</v>
+        <v>90.8</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q21" s="8" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R21" s="11" t="n">
+      <c r="Q21" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R21" s="12" t="n">
         <v>18.1</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2270,10 +2261,10 @@
       <c r="U21" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V21" s="11" t="n">
+      <c r="V21" s="12" t="n">
         <v>18.5</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="12" t="n">
         <v>17</v>
       </c>
       <c r="X21" s="3" t="n">
@@ -2299,43 +2290,43 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>123.3</v>
-      </c>
-      <c r="D22" s="11" t="n">
+        <v>193.3</v>
+      </c>
+      <c r="D22" s="12" t="n">
         <v>20.6</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="12" t="n">
         <v>14.4</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F22" s="12" t="n">
         <v>17.5</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="H22" s="8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H22" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="L22" s="11" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M22" s="15" t="n">
-        <v>1.4</v>
+      <c r="L22" s="12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>91.8</v>
+        <v>91</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>1.8</v>
@@ -2343,7 +2334,7 @@
       <c r="Q22" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="R22" s="11" t="n">
+      <c r="R22" s="12" t="n">
         <v>17.2</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2355,10 +2346,10 @@
       <c r="U22" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="V22" s="11" t="n">
+      <c r="V22" s="12" t="n">
         <v>17.5</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="12" t="n">
         <v>16.9</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2368,7 +2359,7 @@
         <v>947</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>10.9</v>
+        <v>1</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2386,33 +2377,33 @@
       <c r="C23" s="3" t="n">
         <v>177.2</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="12" t="n">
         <v>113.1</v>
       </c>
-      <c r="E23" s="10" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>91.8</v>
+      <c r="E23" s="12" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>91.2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>94.3</v>
+        <v>43.7</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>61.2</v>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="K23" s="10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K23" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="10" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="M23" s="10" t="n">
-        <v>12.2</v>
+      <c r="L23" s="12" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="M23" s="14" t="n">
+        <v>72.2</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>30.4</v>
@@ -2423,14 +2414,14 @@
       <c r="P23" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="Q23" s="10" t="n">
+      <c r="Q23" s="14" t="n">
         <v>109</v>
       </c>
-      <c r="R23" s="11" t="n">
+      <c r="R23" s="12" t="n">
         <v>88.8</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>90.2</v>
+        <v>90.5</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>347.9</v>
@@ -2438,17 +2429,17 @@
       <c r="U23" s="3" t="n">
         <v>40.6</v>
       </c>
-      <c r="V23" s="11" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="W23" s="10" t="n">
+      <c r="V23" s="14" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="W23" s="14" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>9</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>929.5</v>
+        <v>35.5</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>13.8</v>
@@ -2467,22 +2458,22 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>215.4</v>
-      </c>
-      <c r="D24" s="11" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="D24" s="12" t="n">
         <v>22.6</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="12" t="n">
         <v>13.9</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="12" t="n">
         <v>18.3</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>12.9</v>
+        <v>22.9</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>1.5</v>
@@ -2491,27 +2482,27 @@
         <v>1.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L24" s="11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L24" s="12" t="n">
         <v>15.2</v>
       </c>
-      <c r="M24" s="10" t="n">
-        <v>43.4</v>
+      <c r="M24" s="14" t="n">
+        <v>14.4</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>1.4</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>221.1</v>
+        <v>22.1</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q24" s="10" t="n">
+      <c r="Q24" s="14" t="n">
         <v>21.8</v>
       </c>
-      <c r="R24" s="11" t="n">
+      <c r="R24" s="12" t="n">
         <v>17.8</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2523,10 +2514,10 @@
       <c r="U24" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V24" s="11" t="n">
+      <c r="V24" s="12" t="n">
         <v>18.3</v>
       </c>
-      <c r="W24" s="10" t="n">
+      <c r="W24" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2552,16 +2543,16 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="D25" s="11" t="n">
+        <v>400.4</v>
+      </c>
+      <c r="D25" s="12" t="n">
         <v>22.6</v>
       </c>
-      <c r="E25" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>18.8</v>
+      <c r="E25" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>17.8</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>9</v>
@@ -2579,10 +2570,10 @@
         <v>5.9</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="M25" s="15" t="n">
-        <v>84.2</v>
+        <v>15.1</v>
+      </c>
+      <c r="M25" s="12" t="n">
+        <v>14.2</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>1.5</v>
@@ -2591,14 +2582,14 @@
         <v>91.5</v>
       </c>
       <c r="P25" s="3" t="inlineStr"/>
-      <c r="Q25" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="R25" s="8" t="n">
+      <c r="Q25" s="12" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="R25" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>11.6</v>
+        <v>17.6</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>49.5</v>
@@ -2606,10 +2597,10 @@
       <c r="U25" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V25" s="3" t="n">
+      <c r="V25" s="12" t="n">
         <v>16.6</v>
       </c>
-      <c r="W25" s="11" t="n">
+      <c r="W25" s="12" t="n">
         <v>15.9</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2635,22 +2626,22 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="D26" s="11" t="n">
+        <v>326</v>
+      </c>
+      <c r="D26" s="12" t="n">
         <v>22.5</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="12" t="n">
         <v>13.6</v>
       </c>
-      <c r="F26" s="11" t="n">
+      <c r="F26" s="12" t="n">
         <v>18.1</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>8.9</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.4</v>
@@ -2661,14 +2652,14 @@
       <c r="K26" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="L26" s="8" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="M26" s="15" t="n">
-        <v>1.4</v>
+      <c r="L26" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="M26" s="12" t="n">
+        <v>14.1</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>95</v>
@@ -2676,11 +2667,11 @@
       <c r="P26" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="12" t="n">
         <v>20.7</v>
       </c>
-      <c r="R26" s="8" t="n">
-        <v>8.800000000000001</v>
+      <c r="R26" s="12" t="n">
+        <v>17.2</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>17.8</v>
@@ -2691,20 +2682,20 @@
       <c r="U26" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="12" t="n">
         <v>17.9</v>
       </c>
-      <c r="W26" s="11" t="n">
+      <c r="W26" s="12" t="n">
         <v>16.5</v>
       </c>
-      <c r="X26" s="8" t="n">
+      <c r="X26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>88.5</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2720,22 +2711,22 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="D27" s="11" t="n">
+        <v>288.8</v>
+      </c>
+      <c r="D27" s="12" t="n">
         <v>23.5</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E27" s="12" t="n">
         <v>14.4</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F27" s="12" t="n">
         <v>18.9</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>9.1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.4</v>
+        <v>14.9</v>
       </c>
       <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
@@ -2744,14 +2735,14 @@
       <c r="K27" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="L27" s="8" t="n">
+      <c r="L27" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="12" t="n">
         <v>14.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>18.8</v>
+        <v>16.8</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>94</v>
@@ -2759,25 +2750,25 @@
       <c r="P27" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q27" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="R27" s="3" t="n">
+      <c r="Q27" s="12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="R27" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>717</v>
+        <v>77</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V27" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="V27" s="12" t="n">
         <v>17.8</v>
       </c>
-      <c r="W27" s="11" t="n">
+      <c r="W27" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2803,22 +2794,22 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="D28" s="11" t="n">
+        <v>305.9</v>
+      </c>
+      <c r="D28" s="12" t="n">
         <v>21.8</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="E28" s="12" t="n">
         <v>13.8</v>
       </c>
-      <c r="F28" s="11" t="n">
+      <c r="F28" s="12" t="n">
         <v>17.8</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>82.8</v>
+        <v>23.8</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.9</v>
@@ -2826,17 +2817,17 @@
       <c r="J28" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="K28" s="8" t="n">
+      <c r="K28" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="M28" s="12" t="n">
         <v>14.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>18.5</v>
+        <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>95</v>
@@ -2844,10 +2835,10 @@
       <c r="P28" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q28" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R28" s="3" t="n">
+      <c r="Q28" s="12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R28" s="12" t="n">
         <v>17</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2859,20 +2850,20 @@
       <c r="U28" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V28" s="3" t="n">
+      <c r="V28" s="12" t="n">
         <v>16.7</v>
       </c>
-      <c r="W28" s="11" t="n">
+      <c r="W28" s="12" t="n">
         <v>14.8</v>
       </c>
       <c r="X28" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>83.8</v>
+        <v>83</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2890,13 +2881,13 @@
       <c r="C29" s="3" t="n">
         <v>289.8</v>
       </c>
-      <c r="D29" s="11" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F29" s="11" t="n">
+      <c r="D29" s="12" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F29" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="G29" s="3" t="n">
@@ -2906,22 +2897,22 @@
         <v>13.8</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="L29" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L29" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="12" t="n">
         <v>14.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>11.1</v>
+        <v>14.1</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>95</v>
@@ -2929,29 +2920,29 @@
       <c r="P29" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q29" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R29" s="3" t="n">
+      <c r="Q29" s="12" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="R29" s="12" t="n">
         <v>17.8</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="V29" s="12" t="n">
         <v>18.8</v>
       </c>
-      <c r="W29" s="11" t="n">
+      <c r="W29" s="12" t="n">
         <v>17.1</v>
       </c>
-      <c r="X29" s="8" t="n">
-        <v>82.09999999999999</v>
+      <c r="X29" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>85</v>
@@ -2975,34 +2966,34 @@
       <c r="C30" s="3" t="n">
         <v>1609.9</v>
       </c>
-      <c r="D30" s="10" t="n">
-        <v>1129.8</v>
-      </c>
-      <c r="E30" s="14" t="inlineStr"/>
-      <c r="F30" s="10" t="n">
+      <c r="D30" s="14" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="E30" s="13" t="inlineStr"/>
+      <c r="F30" s="14" t="n">
         <v>90.59999999999999</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>49.7</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="K30" s="10" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="L30" s="14" t="inlineStr"/>
-      <c r="M30" s="10" t="n">
-        <v>11.7</v>
+        <v>9.1</v>
+      </c>
+      <c r="K30" s="14" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="L30" s="13" t="inlineStr"/>
+      <c r="M30" s="12" t="n">
+        <v>71.7</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>7.9</v>
+        <v>79.8</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>0.5</v>
@@ -3010,29 +3001,29 @@
       <c r="P30" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="Q30" s="10" t="n">
+      <c r="Q30" s="12" t="n">
         <v>105.2</v>
       </c>
-      <c r="R30" s="10" t="n">
+      <c r="R30" s="12" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>90.09999999999999</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>561</v>
+        <v>361.9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="V30" s="10" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="V30" s="14" t="n">
         <v>88.8</v>
       </c>
-      <c r="W30" s="11" t="n">
+      <c r="W30" s="12" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>88.2</v>
+        <v>88.5</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>441</v>
@@ -3056,13 +3047,13 @@
       <c r="C31" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="12" t="n">
         <v>22.5</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" s="12" t="n">
         <v>13.7</v>
       </c>
-      <c r="F31" s="11" t="n">
+      <c r="F31" s="12" t="n">
         <v>18.1</v>
       </c>
       <c r="G31" s="3" t="n">
@@ -3079,11 +3070,11 @@
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="10" t="n">
-        <v>14.7</v>
+      <c r="M31" s="12" t="n">
+        <v>14.3</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>16.8</v>
@@ -3091,35 +3082,35 @@
       <c r="P31" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" s="10" t="n">
+      <c r="Q31" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="R31" s="10" t="n">
+      <c r="R31" s="12" t="n">
         <v>17.5</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>29.3</v>
+        <v>79.8</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V31" s="10" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="W31" s="11" t="n">
+      <c r="V31" s="12" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="W31" s="12" t="n">
         <v>16.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>1.4</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>119.2</v>
+        <v>19.8</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>214.4</v>
+        <v>24.4</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3135,9 +3126,9 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="D32" s="13" t="inlineStr"/>
+        <v>235.5</v>
+      </c>
+      <c r="D32" s="11" t="inlineStr"/>
       <c r="E32" s="3" t="n">
         <v>14.2</v>
       </c>
@@ -3145,7 +3136,7 @@
         <v>17.9</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>13.4</v>
@@ -3159,14 +3150,14 @@
       <c r="K32" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="L32" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M32" s="15" t="n">
+      <c r="L32" s="12" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="M32" s="9" t="n">
         <v>10.51</v>
       </c>
-      <c r="N32" s="8" t="n">
-        <v>12.8</v>
+      <c r="N32" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>83</v>
@@ -3174,14 +3165,14 @@
       <c r="P32" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q32" s="3" t="n">
+      <c r="Q32" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="R32" s="3" t="n">
-        <v>18.8</v>
+      <c r="R32" s="12" t="n">
+        <v>15.8</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>18.2</v>
+        <v>17</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>90</v>
@@ -3189,20 +3180,20 @@
       <c r="U32" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="V32" s="11" t="n">
+      <c r="V32" s="12" t="n">
         <v>15.9</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="12" t="n">
         <v>15.6</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>18.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>97</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3218,22 +3209,22 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1482.8</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>19.5</v>
+        <v>482.8</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>18.4</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="H33" s="8" t="n">
-        <v>82.59999999999999</v>
+      <c r="H33" s="3" t="n">
+        <v>20.6</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>2.6</v>
@@ -3242,49 +3233,49 @@
         <v>4.9</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="L33" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L33" s="12" t="n">
         <v>13.7</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="N33" s="8" t="n">
-        <v>84.8</v>
+      <c r="N33" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>93</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="12" t="n">
         <v>23.8</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>12.2</v>
+        <v>15.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>21.2</v>
+        <v>51.5</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V33" s="11" t="n">
+      <c r="V33" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="12" t="n">
         <v>15.4</v>
       </c>
-      <c r="X33" s="8" t="n">
+      <c r="X33" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Z33" s="3" t="n">
         <v>4.8</v>
@@ -3305,23 +3296,23 @@
       <c r="C34" s="3" t="n">
         <v>482.8</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="12" t="n">
         <v>24.1</v>
       </c>
-      <c r="E34" s="11" t="n">
+      <c r="E34" s="12" t="n">
         <v>11.5</v>
       </c>
-      <c r="F34" s="11" t="n">
+      <c r="F34" s="12" t="n">
         <v>17.8</v>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="G34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="H34" s="8" t="n">
-        <v>109.5</v>
+      <c r="H34" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.9</v>
@@ -3329,14 +3320,14 @@
       <c r="K34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="12" t="n">
         <v>12.5</v>
       </c>
-      <c r="M34" s="8" t="n">
-        <v>11.6</v>
+      <c r="M34" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>11.1</v>
+        <v>13.1</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>92</v>
@@ -3344,11 +3335,11 @@
       <c r="P34" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="12" t="n">
         <v>23.9</v>
       </c>
-      <c r="R34" s="3" t="n">
-        <v>17.8</v>
+      <c r="R34" s="12" t="n">
+        <v>17.7</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>16.8</v>
@@ -3359,17 +3350,17 @@
       <c r="U34" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V34" s="11" t="n">
+      <c r="V34" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="W34" s="3" t="n">
-        <v>12.8</v>
+      <c r="W34" s="12" t="n">
+        <v>15.8</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -3386,19 +3377,19 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>9492.799999999999</v>
-      </c>
-      <c r="D35" s="11" t="n">
+        <v>492.8</v>
+      </c>
+      <c r="D35" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E35" s="12" t="n">
         <v>13.6</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="F35" s="12" t="n">
         <v>19.3</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1.1</v>
+        <v>11.4</v>
       </c>
       <c r="H35" s="8" t="n">
         <v>279.3</v>
@@ -3412,47 +3403,47 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="12" t="n">
         <v>16.6</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>910</v>
+        <v>10</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q35" s="15" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="R35" s="3" t="n">
+      <c r="Q35" s="12" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="R35" s="12" t="n">
         <v>18.8</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>600.8</v>
+        <v>60</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="V35" s="11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="V35" s="12" t="n">
         <v>20.7</v>
       </c>
-      <c r="W35" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="X35" s="8" t="n">
-        <v>82.8</v>
+      <c r="W35" s="12" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X35" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>125.5</v>
+        <v>75.5</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>6</v>
@@ -3471,19 +3462,19 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>9498.9</v>
-      </c>
-      <c r="D36" s="15" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="E36" s="8" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E36" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="G36" s="8" t="n">
-        <v>410.3</v>
+        <v>12.1</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>10.3</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>12.7</v>
@@ -3497,14 +3488,14 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="15" t="n">
-        <v>86.59999999999999</v>
+      <c r="L36" s="12" t="n">
+        <v>16.6</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="N36" s="8" t="n">
-        <v>17.4</v>
+      <c r="N36" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>91</v>
@@ -3512,35 +3503,35 @@
       <c r="P36" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q36" s="15" t="n">
-        <v>88.09999999999999</v>
-      </c>
-      <c r="R36" s="3" t="n">
+      <c r="Q36" s="12" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="R36" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>52.1</v>
+        <v>55.1</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V36" s="11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="V36" s="12" t="n">
         <v>18.4</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="12" t="n">
         <v>15.9</v>
       </c>
-      <c r="X36" s="8" t="n">
-        <v>66.59999999999999</v>
+      <c r="X36" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3556,15 +3547,15 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2192.8</v>
-      </c>
-      <c r="D37" s="10" t="n">
+        <v>192.8</v>
+      </c>
+      <c r="D37" s="14" t="n">
         <v>119.1</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="14" t="n">
         <v>665.7</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="F37" s="14" t="n">
         <v>9.4</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3572,55 +3563,53 @@
       </c>
       <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="3" t="n">
-        <v>110.6</v>
+        <v>10.6</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="K37" s="10" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="L37" s="10" t="n">
+      <c r="K37" s="14" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="L37" s="12" t="n">
         <v>75.7</v>
       </c>
-      <c r="M37" s="10" t="n">
-        <v>711.2</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>71.59999999999999</v>
-      </c>
+      <c r="M37" s="14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="n">
-        <v>4420.3</v>
+        <v>449</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q37" s="10" t="n">
+      <c r="Q37" s="12" t="n">
         <v>113.4</v>
       </c>
-      <c r="R37" s="10" t="n">
-        <v>81</v>
+      <c r="R37" s="12" t="n">
+        <v>87</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>84.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>313.4</v>
+        <v>13.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>234.8</v>
-      </c>
-      <c r="V37" s="11" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="V37" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="W37" s="10" t="n">
+      <c r="W37" s="12" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>409.8</v>
+        <v>9.5</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>88.40000000000001</v>
@@ -3639,64 +3628,64 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="D38" s="11" t="n">
+        <v>438.6</v>
+      </c>
+      <c r="D38" s="12" t="n">
         <v>23.1</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="12" t="n">
         <v>13.2</v>
       </c>
-      <c r="F38" s="11" t="n">
+      <c r="F38" s="12" t="n">
         <v>18.9</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>12.3</v>
+        <v>22.3</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>12.1</v>
+        <v>2.1</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="10" t="n">
+      <c r="L38" s="14" t="n">
         <v>151.3</v>
       </c>
-      <c r="M38" s="10" t="n">
+      <c r="M38" s="14" t="n">
         <v>14</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>15.2</v>
+        <v>15.5</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q38" s="10" t="n">
+      <c r="Q38" s="12" t="n">
         <v>22.7</v>
       </c>
-      <c r="R38" s="10" t="n">
+      <c r="R38" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>17</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>82.7</v>
+        <v>62.7</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V38" s="11" t="n">
+      <c r="V38" s="12" t="n">
         <v>18.2</v>
       </c>
-      <c r="W38" s="10" t="n">
+      <c r="W38" s="12" t="n">
         <v>16.1</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3722,16 +3711,16 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>39595.3</v>
-      </c>
-      <c r="D39" s="11" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>18.6</v>
+        <v>595.3</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>18.7</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>11.5</v>
@@ -3739,18 +3728,16 @@
       <c r="H39" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="I39" s="3" t="n">
-        <v>13</v>
-      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr"/>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="M39" s="8" t="n">
-        <v>11.5</v>
+      <c r="M39" s="9" t="n">
+        <v>1.5</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>1.6</v>
@@ -3761,14 +3748,14 @@
       <c r="P39" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="12" t="n">
         <v>23.6</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="12" t="n">
         <v>16.6</v>
       </c>
-      <c r="S39" s="8" t="n">
-        <v>20.9</v>
+      <c r="S39" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>52</v>
@@ -3776,11 +3763,11 @@
       <c r="U39" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="V39" s="13" t="inlineStr"/>
+      <c r="V39" s="12" t="inlineStr"/>
       <c r="W39" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="X39" s="8" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X39" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="Y39" s="3" t="n">
@@ -3805,13 +3792,13 @@
       <c r="C40" s="3" t="n">
         <v>545.4</v>
       </c>
-      <c r="D40" s="3" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F40" s="3" t="n">
+      <c r="D40" s="12" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>19.1</v>
       </c>
       <c r="G40" s="3" t="n">
@@ -3826,17 +3813,17 @@
       <c r="J40" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="K40" s="3" t="n">
-        <v>0.8</v>
+      <c r="K40" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M40" s="8" t="n">
-        <v>19</v>
+      <c r="M40" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>1</v>
+        <v>10.7</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>89</v>
@@ -3844,35 +3831,35 @@
       <c r="P40" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="12" t="n">
         <v>23.8</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>58.8</v>
+        <v>58.5</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="12" t="n">
         <v>19.4</v>
       </c>
-      <c r="W40" s="8" t="n">
+      <c r="W40" s="3" t="n">
         <v>16</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>1.6</v>
+        <v>16</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>408.4</v>
+        <v>6.2</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3888,37 +3875,37 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>340.1</v>
-      </c>
-      <c r="D41" s="11" t="n">
+        <v>408.4</v>
+      </c>
+      <c r="D41" s="12" t="n">
         <v>23.7</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E41" s="12" t="n">
         <v>12.5</v>
       </c>
-      <c r="F41" s="11" t="n">
+      <c r="F41" s="12" t="n">
         <v>18.1</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="H41" s="8" t="n">
+      <c r="H41" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15.6</v>
+        <v>13.6</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>19.2</v>
@@ -3929,35 +3916,35 @@
       <c r="P41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="12" t="n">
         <v>23.2</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="S41" s="8" t="n">
+      <c r="S41" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="V41" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="W41" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="T41" s="3" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="X41" s="3" t="n">
-        <v>14.6</v>
+        <v>18.2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>113.8</v>
+        <v>82</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>19.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3973,22 +3960,22 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>331</v>
-      </c>
-      <c r="D42" s="11" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E42" s="11" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="F42" s="11" t="n">
+        <v>340.1</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F42" s="12" t="n">
         <v>18.5</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>11.8</v>
+        <v>13.7</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>1.7</v>
@@ -3996,28 +3983,28 @@
       <c r="J42" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K42" s="3" t="n">
-        <v>0.9</v>
+      <c r="K42" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>16.2</v>
+        <v>14.6</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>15.1</v>
+        <v>13.2</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>16.1</v>
+        <v>19.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" s="3" t="n">
+      <c r="Q42" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="12" t="n">
         <v>16.7</v>
       </c>
       <c r="S42" s="3" t="n">
@@ -4029,20 +4016,20 @@
       <c r="U42" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="V42" s="3" t="n">
-        <v>20.4</v>
+      <c r="V42" s="12" t="n">
+        <v>18.2</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>12.1</v>
+        <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>18.1</v>
+        <v>22.4</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>110.1</v>
+        <v>28</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>58</v>
+        <v>2.6</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4058,76 +4045,76 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>557.1</v>
-      </c>
-      <c r="D43" s="11" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>18</v>
+        <v>537</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>18.1</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>99.59999999999999</v>
+        <v>10.1</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>28.8</v>
+        <v>2.5</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="K43" s="12" t="n">
+        <v>0.1</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="M43" s="8" t="n">
-        <v>35.4</v>
+        <v>16.2</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>15.1</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>1.9</v>
+        <v>16.9</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q43" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q43" s="12" t="n">
         <v>22.2</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="12" t="n">
         <v>16.5</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>12.6</v>
+        <v>15.6</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>186.7</v>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="V43" s="15" t="n">
-        <v>91</v>
-      </c>
-      <c r="W43" s="8" t="n">
-        <v>22.6</v>
+        <v>58</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V43" s="12" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>0</v>
+        <v>557.1</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4143,76 +4130,74 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>2983</v>
-      </c>
-      <c r="D44" s="15" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>10.5</v>
+        <v>22.1</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>18</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>62</v>
+        <v>10.8</v>
       </c>
       <c r="H44" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q44" s="12" t="inlineStr"/>
+      <c r="R44" s="12" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="U44" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="I44" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L44" s="15" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="M44" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="P44" s="8" t="n">
-        <v>340.9</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="R44" s="15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="T44" s="3" t="n">
-        <v>351</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="V44" s="15" t="n">
-        <v>11.15</v>
-      </c>
-      <c r="W44" s="15" t="n">
-        <v>95.5</v>
+      <c r="V44" s="12" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>466.8</v>
+        <v>13.6</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>28.1</v>
+        <v>14.8</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4228,76 +4213,76 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>497</v>
-      </c>
-      <c r="D45" s="11" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F45" s="11" t="n">
-        <v>18.5</v>
+        <v>2983</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>141.7</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>10.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>10.3</v>
+        <v>62</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>11.8</v>
+        <v>70.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>2.5</v>
+        <v>15.2</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K45" s="10" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="K45" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="L45" s="10" t="n">
+      <c r="L45" s="14" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="M45" s="10" t="n">
-        <v>0.6</v>
+      <c r="M45" s="14" t="n">
+        <v>83</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>15.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>10.1</v>
+        <v>540.9</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q45" s="10" t="n">
-        <v>922.8</v>
-      </c>
-      <c r="R45" s="10" t="n">
-        <v>17.1</v>
+        <v>10.6</v>
+      </c>
+      <c r="Q45" s="14" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="R45" s="12" t="n">
+        <v>102.4</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>16.2</v>
+        <v>97.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>58.5</v>
+        <v>351</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="V45" s="10" t="n">
-        <v>118.6</v>
-      </c>
-      <c r="W45" s="10" t="n">
-        <v>15.9</v>
+        <v>69</v>
+      </c>
+      <c r="V45" s="14" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="W45" s="14" t="n">
+        <v>95.90000000000001</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>16.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>82.8</v>
+        <v>468.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>44.8</v>
+        <v>28.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4315,38 +4300,38 @@
       <c r="C46" s="3" t="n">
         <v>497</v>
       </c>
-      <c r="D46" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F46" s="15" t="n">
-        <v>0.1</v>
+      <c r="D46" s="12" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>18.4</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>145.9</v>
+        <v>19.3</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1.7</v>
+        <v>11.8</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>6.9</v>
+        <v>2.5</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L46" s="10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L46" s="14" t="n">
         <v>14.9</v>
       </c>
-      <c r="M46" s="10" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="N46" s="8" t="n">
-        <v>12</v>
+      <c r="M46" s="14" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>90.09999999999999</v>
@@ -4354,35 +4339,35 @@
       <c r="P46" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q46" s="10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R46" s="10" t="n">
-        <v>1.8</v>
+      <c r="Q46" s="12" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="R46" s="12" t="n">
+        <v>17.1</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>1</v>
+        <v>16.2</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>11.8</v>
+        <v>58.5</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>1414</v>
-      </c>
-      <c r="V46" s="10" t="n">
-        <v>117.5</v>
-      </c>
-      <c r="W46" s="10" t="n">
-        <v>11151.1</v>
+        <v>11.5</v>
+      </c>
+      <c r="V46" s="12" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="W46" s="14" t="n">
+        <v>15.9</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0.8</v>
+        <v>55.4</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>15.1</v>
+        <v>11.4</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_correct_values.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_correct_values.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>58.5</v>
+        <v>585.3</v>
       </c>
       <c r="D4" s="12" t="n">
         <v>25</v>
@@ -820,7 +820,7 @@
         <v>14.5</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>2.2</v>
@@ -864,16 +864,16 @@
         <v>388.3</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>2.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>12.3</v>
@@ -982,7 +982,7 @@
         <v>15.9</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>1.2</v>
@@ -994,7 +994,7 @@
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.7</v>
+        <v>17.3</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>18.5</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>22.9</v>
+        <v>229.6</v>
       </c>
       <c r="D7" s="12" t="n">
         <v>21.6</v>
@@ -1049,25 +1049,25 @@
         <v>12.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>29.9</v>
+        <v>27.2</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>40.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>22.4</v>
+        <v>22.9</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.8</v>
@@ -1097,7 +1097,7 @@
         <v>76</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>5.8</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>22.2</v>
+        <v>2224.9</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>11.85</v>
@@ -1146,10 +1146,10 @@
         <v>73.40000000000001</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>60.2</v>
+        <v>60.1</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>166.4</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>59</v>
@@ -1167,7 +1167,7 @@
         <v>86.2</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>12.6</v>
+        <v>312.6</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>53</v>
@@ -1219,7 +1219,7 @@
         <v>12.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>229.5</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>3.3</v>
@@ -1234,7 +1234,7 @@
         <v>13.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>166.4</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>21.8</v>
@@ -1252,10 +1252,10 @@
         <v>17.2</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>21.5</v>
+        <v>62.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="V9" s="14" t="n">
         <v>94</v>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>45</v>
+        <v>145.5</v>
       </c>
       <c r="D10" s="12" t="n">
         <v>23.7</v>
@@ -1313,7 +1313,7 @@
         <v>3.3</v>
       </c>
       <c r="L10" s="14" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="M10" s="14" t="n">
         <v>14.7</v>
@@ -1337,7 +1337,7 @@
         <v>17.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>21.5</v>
+        <v>62.5</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>10.6</v>
@@ -1395,16 +1395,16 @@
         <v>0.7</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="9" t="n">
-        <v>1.5</v>
+        <v>10.2</v>
+      </c>
+      <c r="L11" s="12" t="n">
+        <v>15.3</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>14</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>17.2</v>
+        <v>19.2</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>88</v>
@@ -1422,7 +1422,7 @@
         <v>19</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>212.4</v>
+        <v>22.6</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>55.1</v>
@@ -1472,17 +1472,17 @@
       <c r="K12" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="12" t="n">
         <v>14.3</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>13.5</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>15.9</v>
+        <v>17</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.2</v>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W12" s="11" t="inlineStr"/>
       <c r="X12" s="3" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>940.5</v>
@@ -1553,7 +1553,7 @@
       <c r="K13" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M13" s="12" t="n">
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>32.4</v>
+        <v>324</v>
       </c>
       <c r="D14" s="12" t="n">
         <v>21.8</v>
@@ -1638,7 +1638,7 @@
       <c r="K14" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="12" t="n">
         <v>14.4</v>
       </c>
       <c r="M14" s="12" t="n">
@@ -1681,7 +1681,7 @@
         <v>92</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
       <c r="K15" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" s="12" t="n">
         <v>14.2</v>
       </c>
       <c r="M15" s="12" t="n">
@@ -1733,7 +1733,7 @@
         <v>15.5</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.6</v>
@@ -1751,7 +1751,7 @@
         <v>73</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>18.2</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>147.5</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>14.8</v>
+        <v>1475.2</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>114.8</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>674.7</v>
@@ -1806,19 +1806,19 @@
         <v>6.9</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="L16" s="14" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="L16" s="12" t="n">
         <v>73.2</v>
       </c>
       <c r="M16" s="14" t="n">
         <v>634.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>12.4</v>
+        <v>712.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6</v>
@@ -1826,8 +1826,8 @@
       <c r="Q16" s="12" t="n">
         <v>96.5</v>
       </c>
-      <c r="R16" s="12" t="n">
-        <v>83.5</v>
+      <c r="R16" s="14" t="n">
+        <v>83.2</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>88.09999999999999</v>
@@ -1836,7 +1836,7 @@
         <v>394.5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>24.8</v>
+        <v>24.2</v>
       </c>
       <c r="V16" s="14" t="n">
         <v>84.3</v>
@@ -1848,7 +1848,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>158.8</v>
+        <v>450.2</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1867,16 +1867,16 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>1.2</v>
+        <v>295</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>18.6</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>12.1</v>
+        <v>18.9</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>9.5</v>
@@ -1888,22 +1888,22 @@
         <v>1.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>121.4</v>
+        <v>1.4</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="L17" s="14" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L17" s="12" t="n">
         <v>14.6</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>13.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>15.2</v>
+        <v>2.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>1.2</v>
@@ -1978,7 +1978,7 @@
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="L18" s="3" t="n">
         <v>14</v>
       </c>
       <c r="M18" s="3" t="n">
@@ -2004,7 +2004,7 @@
         <v>69.09999999999999</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="V18" s="12" t="n">
         <v>18.5</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>40.6</v>
+        <v>440.6</v>
       </c>
       <c r="D19" s="12" t="n">
         <v>25</v>
@@ -2047,7 +2047,7 @@
         <v>19.5</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>12.1</v>
@@ -2061,7 +2061,7 @@
       <c r="K19" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="L19" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="M19" s="3" t="n">
@@ -2074,7 +2074,7 @@
         <v>92</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>24.9</v>
@@ -2123,7 +2123,7 @@
         <v>153.1</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>20.7</v>
+        <v>20</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>13.8</v>
@@ -2132,7 +2132,7 @@
         <v>17.3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8.9</v>
+        <v>19.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>13.8</v>
@@ -2141,19 +2141,19 @@
         <v>1.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="L20" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="M20" s="9" t="n">
         <v>45.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>17.8</v>
+        <v>14.8</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
@@ -2174,7 +2174,7 @@
         <v>76.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>5.7</v>
+        <v>2.2</v>
       </c>
       <c r="V20" s="12" t="n">
         <v>17.6</v>
@@ -2205,7 +2205,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>251.7</v>
+        <v>261.7</v>
       </c>
       <c r="D21" s="12" t="n">
         <v>21.9</v>
@@ -2231,14 +2231,14 @@
       <c r="K21" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="L21" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1.6</v>
+        <v>16.2</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>90.8</v>
@@ -2316,14 +2316,14 @@
       <c r="K22" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="L22" s="12" t="n">
-        <v>15.5</v>
+      <c r="L22" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.1</v>
+        <v>16.1</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>91</v>
@@ -2390,7 +2390,7 @@
         <v>43.7</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>61.2</v>
+        <v>61.3</v>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
@@ -2399,7 +2399,7 @@
       <c r="K23" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="L23" s="14" t="n">
         <v>76.2</v>
       </c>
       <c r="M23" s="14" t="n">
@@ -2421,7 +2421,7 @@
         <v>88.8</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>90.5</v>
+        <v>90.3</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>347.9</v>
@@ -2430,7 +2430,7 @@
         <v>40.6</v>
       </c>
       <c r="V23" s="14" t="n">
-        <v>91.3</v>
+        <v>22.8</v>
       </c>
       <c r="W23" s="14" t="n">
         <v>81.09999999999999</v>
@@ -2439,7 +2439,7 @@
         <v>9</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>35.5</v>
+        <v>435.5</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>13.8</v>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>29.5</v>
+        <v>295.4</v>
       </c>
       <c r="D24" s="12" t="n">
         <v>22.6</v>
@@ -2473,7 +2473,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>22.9</v>
+        <v>12.9</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>1.5</v>
@@ -2482,19 +2482,19 @@
         <v>1.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L24" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L24" s="14" t="n">
         <v>15.2</v>
       </c>
       <c r="M24" s="14" t="n">
         <v>14.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.4</v>
+        <v>16</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>22.1</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>1.4</v>
@@ -2566,7 +2566,7 @@
       <c r="J25" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="12" t="n">
         <v>5.9</v>
       </c>
       <c r="L25" s="3" t="n">
@@ -2576,7 +2576,7 @@
         <v>14.2</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1.5</v>
+        <v>15.7</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>91.5</v>
@@ -2649,8 +2649,8 @@
       <c r="J26" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>3.9</v>
+      <c r="K26" s="12" t="n">
+        <v>3.5</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>14.6</v>
@@ -2659,7 +2659,7 @@
         <v>14.1</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.5</v>
+        <v>15.8</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>95</v>
@@ -2671,7 +2671,7 @@
         <v>20.7</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>17.8</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>288.8</v>
+        <v>287.8</v>
       </c>
       <c r="D27" s="12" t="n">
         <v>23.5</v>
@@ -2732,7 +2732,7 @@
       <c r="J27" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="12" t="n">
         <v>10.8</v>
       </c>
       <c r="L27" s="3" t="n">
@@ -2809,7 +2809,7 @@
         <v>8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>23.8</v>
+        <v>13.8</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.9</v>
@@ -2817,7 +2817,7 @@
       <c r="J28" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="12" t="n">
         <v>15.4</v>
       </c>
       <c r="L28" s="3" t="n">
@@ -2894,7 +2894,7 @@
         <v>8.1</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>13.8</v>
+        <v>33.8</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1.3</v>
@@ -2902,8 +2902,8 @@
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K29" s="3" t="n">
-        <v>1.8</v>
+      <c r="K29" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>14.9</v>
@@ -2912,7 +2912,7 @@
         <v>14.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>14.1</v>
+        <v>21.2</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>95</v>
@@ -2921,7 +2921,7 @@
         <v>0.8</v>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="R29" s="12" t="n">
         <v>17.8</v>
@@ -2985,7 +2985,7 @@
       <c r="J30" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="K30" s="14" t="n">
+      <c r="K30" s="12" t="n">
         <v>35.6</v>
       </c>
       <c r="L30" s="13" t="inlineStr"/>
@@ -2993,7 +2993,7 @@
         <v>71.7</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>79.8</v>
+        <v>79.2</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>0.5</v>
@@ -3011,13 +3011,13 @@
         <v>90.09999999999999</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>361.9</v>
+        <v>361.2</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>34.6</v>
       </c>
-      <c r="V30" s="14" t="n">
-        <v>88.8</v>
+      <c r="V30" s="12" t="n">
+        <v>87.8</v>
       </c>
       <c r="W30" s="12" t="n">
         <v>81.09999999999999</v>
@@ -3074,10 +3074,10 @@
         <v>14.3</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>16.8</v>
+        <v>16</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>1</v>
@@ -3089,10 +3089,10 @@
         <v>17.5</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>18.1</v>
+        <v>181.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>79.8</v>
+        <v>72.3</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>6.9</v>
@@ -3110,7 +3110,7 @@
         <v>19.8</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>24.4</v>
+        <v>10.4</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3128,11 +3128,13 @@
       <c r="C32" s="3" t="n">
         <v>235.5</v>
       </c>
-      <c r="D32" s="11" t="inlineStr"/>
-      <c r="E32" s="3" t="n">
+      <c r="D32" s="12" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="E32" s="12" t="n">
         <v>14.2</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="G32" s="3" t="n">
@@ -3147,7 +3149,7 @@
       <c r="J32" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="12" t="n">
         <v>12.7</v>
       </c>
       <c r="L32" s="12" t="n">
@@ -3157,7 +3159,7 @@
         <v>10.51</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.2</v>
+        <v>11.2</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>83</v>
@@ -3172,13 +3174,13 @@
         <v>15.8</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>90</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="V32" s="12" t="n">
         <v>15.9</v>
@@ -3193,7 +3195,7 @@
         <v>97</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3209,22 +3211,22 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>482.8</v>
+        <v>1482.8</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>11.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>20.6</v>
+        <v>26.6</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>2.6</v>
@@ -3232,8 +3234,8 @@
       <c r="J33" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K33" s="3" t="n">
-        <v>1.8</v>
+      <c r="K33" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>13.7</v>
@@ -3242,7 +3244,7 @@
         <v>13</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>1.4</v>
+        <v>14</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>93</v>
@@ -3309,7 +3311,7 @@
         <v>12.6</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.3</v>
@@ -3317,7 +3319,7 @@
       <c r="J34" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="12" t="n">
@@ -3357,7 +3359,7 @@
         <v>15.8</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="Y34" s="3" t="n">
         <v>81</v>
@@ -3400,7 +3402,7 @@
       <c r="J35" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="12" t="n">
@@ -3410,10 +3412,10 @@
         <v>15.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>11.6</v>
+        <v>17.6</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>2</v>
@@ -3462,16 +3464,16 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="D36" s="3" t="n">
+        <v>498.9</v>
+      </c>
+      <c r="D36" s="12" t="n">
         <v>24.2</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="12" t="n">
         <v>13.9</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>12.1</v>
+      <c r="F36" s="12" t="n">
+        <v>19.1</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>10.3</v>
@@ -3485,7 +3487,7 @@
       <c r="J36" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="12" t="n">
@@ -3495,7 +3497,7 @@
         <v>15.6</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>18.2</v>
+        <v>17.2</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>91</v>
@@ -3528,10 +3530,10 @@
         <v>16.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>79.8</v>
+        <v>79</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3547,7 +3549,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>192.8</v>
+        <v>2192.8</v>
       </c>
       <c r="D37" s="14" t="n">
         <v>119.1</v>
@@ -3568,7 +3570,7 @@
       <c r="J37" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="K37" s="14" t="n">
+      <c r="K37" s="12" t="n">
         <v>12.7</v>
       </c>
       <c r="L37" s="12" t="n">
@@ -3594,7 +3596,7 @@
         <v>84.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>13.4</v>
+        <v>313.4</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>54.8</v>
@@ -3606,10 +3608,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>85.5</v>
+        <v>85.3</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>9.5</v>
+        <v>409.2</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>88.40000000000001</v>
@@ -3631,19 +3633,19 @@
         <v>438.6</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>23.1</v>
+        <v>23.8</v>
       </c>
       <c r="E38" s="12" t="n">
         <v>13.2</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>22.3</v>
+        <v>12.3</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>2.1</v>
@@ -3659,10 +3661,10 @@
         <v>14</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>11.8</v>
+        <v>0.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>15.5</v>
+        <v>15.2</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>1.8</v>
@@ -3728,16 +3730,18 @@
       <c r="H39" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="I39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="M39" s="9" t="n">
-        <v>1.5</v>
+        <v>28.8</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>11.5</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>1.6</v>
@@ -3763,8 +3767,8 @@
       <c r="U39" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="V39" s="12" t="inlineStr"/>
-      <c r="W39" s="3" t="n">
+      <c r="V39" s="11" t="inlineStr"/>
+      <c r="W39" s="12" t="n">
         <v>15.7</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3793,7 +3797,7 @@
         <v>545.4</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="E40" s="12" t="n">
         <v>13.8</v>
@@ -3802,7 +3806,7 @@
         <v>19.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>10.7</v>
+        <v>22.6</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>11.5</v>
@@ -3823,7 +3827,7 @@
         <v>15</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>10.7</v>
+        <v>10.1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>89</v>
@@ -3846,14 +3850,14 @@
       <c r="U40" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V40" s="12" t="n">
+      <c r="V40" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="W40" s="3" t="n">
+      <c r="W40" s="12" t="n">
         <v>16</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>82</v>
@@ -3881,7 +3885,7 @@
         <v>23.7</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="F41" s="12" t="n">
         <v>18.1</v>
@@ -3929,13 +3933,13 @@
         <v>62.5</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="V41" s="12" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="V41" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="W41" s="3" t="n">
-        <v>18</v>
+      <c r="W41" s="12" t="n">
+        <v>17</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>18.2</v>
@@ -3966,7 +3970,7 @@
         <v>22.4</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>14.6</v>
+        <v>14.1</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>18.5</v>
@@ -3990,7 +3994,7 @@
         <v>14.6</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>13.2</v>
+        <v>22.6</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>19.2</v>
@@ -4016,17 +4020,17 @@
       <c r="U42" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="V42" s="12" t="n">
+      <c r="V42" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>22.4</v>
+        <v>18.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>2.6</v>
@@ -4078,7 +4082,7 @@
         <v>15.1</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>16.9</v>
+        <v>16.2</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>92</v>
@@ -4101,11 +4105,11 @@
       <c r="U43" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="V43" s="12" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>15.8</v>
+      <c r="V43" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="W43" s="12" t="n">
+        <v>15.2</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>4.2</v>
@@ -4130,7 +4134,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>22.1</v>
+        <v>237.1</v>
       </c>
       <c r="D44" s="12" t="n">
         <v>23.4</v>
@@ -4163,7 +4167,7 @@
         <v>13.4</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>11.4</v>
+        <v>19.2</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>91</v>
@@ -4176,7 +4180,7 @@
         <v>16.7</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>15.9</v>
+        <v>16.9</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>59.5</v>
@@ -4184,10 +4188,10 @@
       <c r="U44" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="V44" s="12" t="n">
+      <c r="V44" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="W44" s="3" t="n">
+      <c r="W44" s="12" t="n">
         <v>14.5</v>
       </c>
       <c r="X44" s="3" t="n">
@@ -4219,7 +4223,7 @@
         <v>141.7</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>97.09999999999999</v>
+        <v>797.1</v>
       </c>
       <c r="F45" s="14" t="n">
         <v>10.5</v>
@@ -4246,7 +4250,7 @@
         <v>83</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>540.9</v>
@@ -4255,7 +4259,7 @@
         <v>10.6</v>
       </c>
       <c r="Q45" s="14" t="n">
-        <v>12.7</v>
+        <v>13.7</v>
       </c>
       <c r="R45" s="12" t="n">
         <v>102.4</v>
@@ -4273,13 +4277,13 @@
         <v>111.5</v>
       </c>
       <c r="W45" s="14" t="n">
-        <v>95.90000000000001</v>
+        <v>22.2</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>468.8</v>
+        <v>466.8</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>28.7</v>
@@ -4310,7 +4314,7 @@
         <v>18.4</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>19.3</v>
+        <v>10.3</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>11.8</v>
@@ -4322,13 +4326,13 @@
         <v>4.4</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="L46" s="14" t="n">
         <v>14.9</v>
       </c>
       <c r="M46" s="14" t="n">
-        <v>20.4</v>
+        <v>8</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>15.2</v>
@@ -4354,17 +4358,17 @@
       <c r="U46" s="3" t="n">
         <v>11.5</v>
       </c>
-      <c r="V46" s="12" t="n">
+      <c r="V46" s="14" t="n">
         <v>18.6</v>
       </c>
-      <c r="W46" s="14" t="n">
+      <c r="W46" s="12" t="n">
         <v>15.9</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>55.4</v>
+        <v>11.4</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>11.4</v>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_correct_values.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_correct_values.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>585.3</v>
+        <v>58.5</v>
       </c>
       <c r="D4" s="12" t="n">
         <v>25</v>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>388.3</v>
+        <v>38.8</v>
       </c>
       <c r="D5" s="12" t="n">
         <v>23.9</v>
@@ -888,13 +888,13 @@
         <v>15.7</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>0</v>
@@ -979,10 +979,10 @@
         <v>13.6</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>15.9</v>
+        <v>1.5</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>22</v>
+        <v>22.4</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>1.2</v>
@@ -994,7 +994,7 @@
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>17.3</v>
+        <v>1.7</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>18.5</v>
@@ -1049,7 +1049,7 @@
         <v>12.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>1.8</v>
@@ -1067,7 +1067,7 @@
         <v>40.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>22.9</v>
+        <v>20</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.8</v>
@@ -1097,7 +1097,7 @@
         <v>76</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>5.8</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2224.9</v>
+        <v>222.9</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>11.85</v>
@@ -1146,10 +1146,10 @@
         <v>73.40000000000001</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>60.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>166.4</v>
+        <v>16.4</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>59</v>
@@ -1219,7 +1219,7 @@
         <v>12.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>229.5</v>
+        <v>22.5</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>3.3</v>
@@ -1234,7 +1234,7 @@
         <v>13.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>166.4</v>
+        <v>16.4</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>21.8</v>
@@ -1255,7 +1255,7 @@
         <v>62.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="V9" s="14" t="n">
         <v>94</v>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>145.5</v>
+        <v>145</v>
       </c>
       <c r="D10" s="12" t="n">
         <v>23.7</v>
@@ -1301,10 +1301,10 @@
         <v>10.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.2</v>
+        <v>21.2</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>6.2</v>
+        <v>0.2</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>21.3</v>
@@ -1313,7 +1313,7 @@
         <v>3.3</v>
       </c>
       <c r="L10" s="14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="14" t="n">
         <v>14.7</v>
@@ -1395,7 +1395,7 @@
         <v>0.7</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>15.3</v>
@@ -1404,7 +1404,7 @@
         <v>14</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>88</v>
@@ -1422,7 +1422,7 @@
         <v>19</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>22.6</v>
+        <v>2</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>55.1</v>
@@ -1449,10 +1449,10 @@
         <v>229.5</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>17.9</v>
@@ -1479,7 +1479,7 @@
         <v>13.5</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>92</v>
@@ -1648,7 +1648,7 @@
         <v>15.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>1</v>
@@ -1700,10 +1700,10 @@
         <v>307.9</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>18.9</v>
@@ -1782,16 +1782,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1475.2</v>
+        <v>147.5</v>
       </c>
       <c r="D16" s="12" t="n">
         <v>114.8</v>
       </c>
-      <c r="E16" s="14" t="n">
-        <v>674.7</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>92.2</v>
+      <c r="E16" s="12" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>91.2</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>47.4</v>
@@ -1815,7 +1815,7 @@
         <v>634.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>712.4</v>
+        <v>12.4</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>14.5</v>
@@ -1826,8 +1826,8 @@
       <c r="Q16" s="12" t="n">
         <v>96.5</v>
       </c>
-      <c r="R16" s="14" t="n">
-        <v>83.2</v>
+      <c r="R16" s="12" t="n">
+        <v>83.5</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>88.09999999999999</v>
@@ -1836,7 +1836,7 @@
         <v>394.5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>24.2</v>
+        <v>24.8</v>
       </c>
       <c r="V16" s="14" t="n">
         <v>84.3</v>
@@ -1848,7 +1848,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>450.2</v>
+        <v>450</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1869,14 +1869,14 @@
       <c r="C17" s="3" t="n">
         <v>295</v>
       </c>
-      <c r="D17" s="14" t="n">
-        <v>28</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>18.9</v>
+      <c r="D17" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>18.3</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>9.5</v>
@@ -1891,7 +1891,7 @@
         <v>1.4</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>10.2</v>
+        <v>20.2</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>14.6</v>
@@ -1900,10 +1900,10 @@
         <v>13.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>1.2</v>
@@ -1978,7 +1978,7 @@
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M18" s="3" t="n">
@@ -2004,7 +2004,7 @@
         <v>69.09999999999999</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="V18" s="12" t="n">
         <v>18.5</v>
@@ -2047,7 +2047,7 @@
         <v>19.5</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>12.1</v>
@@ -2061,7 +2061,7 @@
       <c r="K19" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="12" t="n">
         <v>15.1</v>
       </c>
       <c r="M19" s="3" t="n">
@@ -2074,7 +2074,7 @@
         <v>92</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>24.9</v>
@@ -2123,7 +2123,7 @@
         <v>153.1</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>20</v>
+        <v>20.7</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>13.8</v>
@@ -2132,7 +2132,7 @@
         <v>17.3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>19.9</v>
+        <v>0.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>13.8</v>
@@ -2146,14 +2146,14 @@
       <c r="K20" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="12" t="n">
         <v>15.4</v>
       </c>
       <c r="M20" s="9" t="n">
         <v>45.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>14.8</v>
+        <v>17.8</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
@@ -2174,7 +2174,7 @@
         <v>76.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="V20" s="12" t="n">
         <v>17.6</v>
@@ -2231,14 +2231,14 @@
       <c r="K21" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="12" t="n">
         <v>16.2</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>16.2</v>
+        <v>16.8</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>90.8</v>
@@ -2316,14 +2316,14 @@
       <c r="K22" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="L22" s="3" t="n">
-        <v>22</v>
+      <c r="L22" s="12" t="n">
+        <v>15.5</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>16.1</v>
+        <v>16.5</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>91</v>
@@ -2384,22 +2384,22 @@
         <v>69.40000000000001</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>91.2</v>
+        <v>91.3</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>43.7</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>61.3</v>
+        <v>64.3</v>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K23" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="14" t="n">
+      <c r="L23" s="12" t="n">
         <v>76.2</v>
       </c>
       <c r="M23" s="14" t="n">
@@ -2430,7 +2430,7 @@
         <v>40.6</v>
       </c>
       <c r="V23" s="14" t="n">
-        <v>22.8</v>
+        <v>91.3</v>
       </c>
       <c r="W23" s="14" t="n">
         <v>81.09999999999999</v>
@@ -2484,17 +2484,17 @@
       <c r="K24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L24" s="14" t="n">
+      <c r="L24" s="12" t="n">
         <v>15.2</v>
       </c>
       <c r="M24" s="14" t="n">
         <v>14.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>1.4</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>400.4</v>
+        <v>40</v>
       </c>
       <c r="D25" s="12" t="n">
         <v>22.6</v>
@@ -2742,7 +2742,7 @@
         <v>14.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>16.8</v>
+        <v>11.8</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>94</v>
@@ -2809,7 +2809,7 @@
         <v>8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>13.8</v>
+        <v>83.8</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.9</v>
@@ -2860,7 +2860,7 @@
         <v>15.8</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>83</v>
+        <v>83.8</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>3.2</v>
@@ -2912,7 +2912,7 @@
         <v>14.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>21.2</v>
+        <v>1.6</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>95</v>
@@ -2966,8 +2966,8 @@
       <c r="C30" s="3" t="n">
         <v>1609.9</v>
       </c>
-      <c r="D30" s="14" t="n">
-        <v>112.9</v>
+      <c r="D30" s="12" t="n">
+        <v>112.5</v>
       </c>
       <c r="E30" s="13" t="inlineStr"/>
       <c r="F30" s="14" t="n">
@@ -3011,7 +3011,7 @@
         <v>90.09999999999999</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>361.2</v>
+        <v>36.1</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>34.6</v>
@@ -3074,7 +3074,7 @@
         <v>14.3</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>16</v>
@@ -3089,7 +3089,7 @@
         <v>17.5</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>181.1</v>
+        <v>181.2</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>72.3</v>
@@ -3110,7 +3110,7 @@
         <v>19.8</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>10.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
       <c r="E32" s="12" t="n">
         <v>14.2</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="F32" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="G32" s="3" t="n">
@@ -3159,7 +3159,7 @@
         <v>10.51</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>11.2</v>
+        <v>1.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>83</v>
@@ -3180,7 +3180,7 @@
         <v>90</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="V32" s="12" t="n">
         <v>15.9</v>
@@ -3195,7 +3195,7 @@
         <v>97</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3211,22 +3211,22 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1482.8</v>
+        <v>482.8</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>11.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>26.6</v>
+        <v>28.6</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>2.6</v>
@@ -3244,7 +3244,7 @@
         <v>13</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>14</v>
+        <v>1.4</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>93</v>
@@ -3329,7 +3329,7 @@
         <v>19.6</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>13.1</v>
+        <v>1.3</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>92</v>
@@ -3412,7 +3412,7 @@
         <v>15.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>17.6</v>
+        <v>1.7</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>90</v>
@@ -3427,7 +3427,7 @@
         <v>18.8</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>60</v>
@@ -3467,7 +3467,7 @@
         <v>498.9</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="E36" s="12" t="n">
         <v>13.9</v>
@@ -3533,7 +3533,7 @@
         <v>79</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>85.3</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>409.2</v>
+        <v>409</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>88.40000000000001</v>
@@ -3642,7 +3642,7 @@
         <v>18.5</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>12.3</v>
@@ -3730,21 +3730,19 @@
       <c r="H39" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="I39" s="3" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>11.5</v>
+        <v>16</v>
+      </c>
+      <c r="M39" s="9" t="n">
+        <v>1.5</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>1.6</v>
+        <v>30.1</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>94</v>
@@ -3806,7 +3804,7 @@
         <v>19.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>22.6</v>
+        <v>10.7</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>11.5</v>
@@ -3827,7 +3825,7 @@
         <v>15</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>10.1</v>
+        <v>1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>89</v>
@@ -3857,10 +3855,10 @@
         <v>16</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>6.2</v>
@@ -3885,7 +3883,7 @@
         <v>23.7</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="F41" s="12" t="n">
         <v>18.1</v>
@@ -3912,7 +3910,7 @@
         <v>13.6</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>19.2</v>
+        <v>19.8</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>88.90000000000001</v>
@@ -3939,7 +3937,7 @@
         <v>19</v>
       </c>
       <c r="W41" s="12" t="n">
-        <v>17</v>
+        <v>17.8</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>18.2</v>
@@ -3994,7 +3992,7 @@
         <v>14.6</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>22.6</v>
+        <v>13.3</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>19.2</v>
@@ -4030,7 +4028,7 @@
         <v>18.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>2.6</v>
@@ -4134,7 +4132,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>237.1</v>
+        <v>2</v>
       </c>
       <c r="D44" s="12" t="n">
         <v>23.4</v>
@@ -4167,7 +4165,7 @@
         <v>13.4</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>19.2</v>
+        <v>1.4</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>91</v>
@@ -4180,7 +4178,7 @@
         <v>16.7</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>16.9</v>
+        <v>15.9</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>59.5</v>
@@ -4217,7 +4215,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2983</v>
+        <v>298</v>
       </c>
       <c r="D45" s="12" t="n">
         <v>141.7</v>
@@ -4277,7 +4275,7 @@
         <v>111.5</v>
       </c>
       <c r="W45" s="14" t="n">
-        <v>22.2</v>
+        <v>95.5</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>99.59999999999999</v>
@@ -4326,13 +4324,13 @@
         <v>4.4</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="14" t="n">
         <v>14.9</v>
       </c>
       <c r="M46" s="14" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>15.2</v>
@@ -4365,13 +4363,13 @@
         <v>15.9</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="Y46" s="3" t="n">
         <v>19</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
